--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122699990</v>
+        <v>122700013</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524886</v>
+        <v>524981</v>
       </c>
       <c r="R2" t="n">
-        <v>7020196</v>
+        <v>7020231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122699987</v>
+        <v>122700032</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524637</v>
+        <v>525024</v>
       </c>
       <c r="R3" t="n">
-        <v>7020366</v>
+        <v>7020263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122699999</v>
+        <v>122699995</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524951</v>
+        <v>524719</v>
       </c>
       <c r="R4" t="n">
-        <v>7020351</v>
+        <v>7020350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700019</v>
+        <v>122699986</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1030,16 +1025,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525451</v>
+        <v>525217</v>
       </c>
       <c r="R5" t="n">
-        <v>7020169</v>
+        <v>7020178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700031</v>
+        <v>122700025</v>
       </c>
       <c r="B6" t="n">
-        <v>90855</v>
+        <v>79741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524640</v>
+        <v>525407</v>
       </c>
       <c r="R6" t="n">
-        <v>7020358</v>
+        <v>7020146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700035</v>
+        <v>122699999</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525057</v>
+        <v>524951</v>
       </c>
       <c r="R7" t="n">
-        <v>7020101</v>
+        <v>7020351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700030</v>
+        <v>122700026</v>
       </c>
       <c r="B8" t="n">
         <v>79741</v>
@@ -1347,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524857</v>
+        <v>525299</v>
       </c>
       <c r="R8" t="n">
-        <v>7020120</v>
+        <v>7019885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122699986</v>
+        <v>122700001</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1550,24 +1558,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525217</v>
+        <v>525052</v>
       </c>
       <c r="R10" t="n">
-        <v>7020178</v>
+        <v>7020331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,7 +1631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700014</v>
+        <v>122700004</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524981</v>
+        <v>525112</v>
       </c>
       <c r="R11" t="n">
-        <v>7020235</v>
+        <v>7020339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700007</v>
+        <v>122700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,16 +1754,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525106</v>
+        <v>524639</v>
       </c>
       <c r="R12" t="n">
-        <v>7020311</v>
+        <v>7020328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700022</v>
+        <v>122700012</v>
       </c>
       <c r="B13" t="n">
-        <v>90848</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,25 +1857,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525086</v>
+        <v>524986</v>
       </c>
       <c r="R13" t="n">
-        <v>7019775</v>
+        <v>7020251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,6 +1921,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,7 +1952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122699995</v>
+        <v>122700005</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524719</v>
+        <v>525103</v>
       </c>
       <c r="R14" t="n">
-        <v>7020350</v>
+        <v>7020335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,7 +2032,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2059,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700020</v>
+        <v>122699988</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525498</v>
+        <v>524640</v>
       </c>
       <c r="R15" t="n">
-        <v>7020014</v>
+        <v>7020358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700029</v>
+        <v>122700007</v>
       </c>
       <c r="B16" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2182,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525339</v>
+        <v>525106</v>
       </c>
       <c r="R16" t="n">
-        <v>7020046</v>
+        <v>7020311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,6 +2242,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700027</v>
+        <v>122700035</v>
       </c>
       <c r="B17" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2303,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525364</v>
+        <v>525057</v>
       </c>
       <c r="R17" t="n">
-        <v>7020041</v>
+        <v>7020101</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2375,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122699989</v>
+        <v>122700015</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2405,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524846</v>
+        <v>524981</v>
       </c>
       <c r="R18" t="n">
-        <v>7020185</v>
+        <v>7020235</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,7 +2482,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700009</v>
+        <v>122700019</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2512,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525066</v>
+        <v>525451</v>
       </c>
       <c r="R19" t="n">
-        <v>7020292</v>
+        <v>7020169</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700024</v>
+        <v>122700030</v>
       </c>
       <c r="B20" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,21 +2605,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524639</v>
+        <v>524857</v>
       </c>
       <c r="R20" t="n">
-        <v>7020328</v>
+        <v>7020120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,11 +2665,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700005</v>
+        <v>122700034</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2726,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525103</v>
+        <v>525015</v>
       </c>
       <c r="R21" t="n">
-        <v>7020335</v>
+        <v>7019776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,11 +2767,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700036</v>
+        <v>122700029</v>
       </c>
       <c r="B22" t="n">
-        <v>90855</v>
+        <v>79741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524700</v>
+        <v>525339</v>
       </c>
       <c r="R22" t="n">
-        <v>7020267</v>
+        <v>7020046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700028</v>
+        <v>122699997</v>
       </c>
       <c r="B23" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525342</v>
+        <v>524808</v>
       </c>
       <c r="R23" t="n">
-        <v>7020049</v>
+        <v>7020420</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,6 +2971,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,7 +3002,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122699996</v>
+        <v>122700006</v>
       </c>
       <c r="B24" t="n">
         <v>57384</v>
@@ -3037,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524805</v>
+        <v>525089</v>
       </c>
       <c r="R24" t="n">
-        <v>7020421</v>
+        <v>7020329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3109,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700003</v>
+        <v>122699991</v>
       </c>
       <c r="B25" t="n">
         <v>57384</v>
@@ -3144,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525101</v>
+        <v>524850</v>
       </c>
       <c r="R25" t="n">
-        <v>7020350</v>
+        <v>7020302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,7 +3189,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,7 +3216,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700032</v>
+        <v>122700031</v>
       </c>
       <c r="B26" t="n">
         <v>90855</v>
@@ -3251,10 +3256,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525024</v>
+        <v>524640</v>
       </c>
       <c r="R26" t="n">
-        <v>7020263</v>
+        <v>7020358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700025</v>
+        <v>122699996</v>
       </c>
       <c r="B27" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3329,21 +3334,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525407</v>
+        <v>524805</v>
       </c>
       <c r="R27" t="n">
-        <v>7020146</v>
+        <v>7020421</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3389,6 +3394,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3415,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700006</v>
+        <v>122700009</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -3455,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525089</v>
+        <v>525066</v>
       </c>
       <c r="R28" t="n">
-        <v>7020329</v>
+        <v>7020292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700034</v>
+        <v>122700008</v>
       </c>
       <c r="B29" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3538,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3562,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525015</v>
+        <v>525081</v>
       </c>
       <c r="R29" t="n">
-        <v>7019776</v>
+        <v>7020283</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,6 +3608,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700000</v>
+        <v>122699987</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -3664,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524963</v>
+        <v>524637</v>
       </c>
       <c r="R30" t="n">
-        <v>7020373</v>
+        <v>7020366</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,7 +3719,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3731,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700026</v>
+        <v>122700036</v>
       </c>
       <c r="B31" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,21 +3762,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3771,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525299</v>
+        <v>524700</v>
       </c>
       <c r="R31" t="n">
-        <v>7019885</v>
+        <v>7020267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3848,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122699997</v>
+        <v>122699998</v>
       </c>
       <c r="B32" t="n">
         <v>57384</v>
@@ -3873,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524808</v>
+        <v>524855</v>
       </c>
       <c r="R32" t="n">
-        <v>7020420</v>
+        <v>7020387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700016</v>
+        <v>122700033</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,21 +3971,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3980,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524970</v>
+        <v>525450</v>
       </c>
       <c r="R33" t="n">
-        <v>7020222</v>
+        <v>7019935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,11 +4031,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4047,7 +4057,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699991</v>
+        <v>122699990</v>
       </c>
       <c r="B34" t="n">
         <v>57384</v>
@@ -4087,10 +4097,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524850</v>
+        <v>524886</v>
       </c>
       <c r="R34" t="n">
-        <v>7020302</v>
+        <v>7020196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,7 +4137,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4154,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699988</v>
+        <v>122700037</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4180,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524640</v>
+        <v>524743</v>
       </c>
       <c r="R35" t="n">
-        <v>7020358</v>
+        <v>7020378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4230,11 +4240,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4261,10 +4266,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700010</v>
+        <v>122700027</v>
       </c>
       <c r="B36" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,21 +4282,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4301,10 +4306,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525061</v>
+        <v>525364</v>
       </c>
       <c r="R36" t="n">
-        <v>7020296</v>
+        <v>7020041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,11 +4342,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700002</v>
+        <v>122700039</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4384,21 +4384,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525076</v>
+        <v>525354</v>
       </c>
       <c r="R37" t="n">
-        <v>7020349</v>
+        <v>7019963</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,11 +4444,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,7 +4470,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700013</v>
+        <v>122700017</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -4515,10 +4510,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524981</v>
+        <v>524976</v>
       </c>
       <c r="R38" t="n">
-        <v>7020231</v>
+        <v>7020218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,10 +4577,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700017</v>
+        <v>122700022</v>
       </c>
       <c r="B39" t="n">
-        <v>57384</v>
+        <v>90848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,25 +4589,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4622,10 +4617,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524976</v>
+        <v>525086</v>
       </c>
       <c r="R39" t="n">
-        <v>7020218</v>
+        <v>7019775</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,11 +4653,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4689,7 +4679,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700018</v>
+        <v>122700020</v>
       </c>
       <c r="B40" t="n">
         <v>57384</v>
@@ -4729,10 +4719,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525314</v>
+        <v>525498</v>
       </c>
       <c r="R40" t="n">
-        <v>7020173</v>
+        <v>7020014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,10 +4786,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700033</v>
+        <v>122700003</v>
       </c>
       <c r="B41" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4812,21 +4802,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4836,10 +4826,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525450</v>
+        <v>525101</v>
       </c>
       <c r="R41" t="n">
-        <v>7019935</v>
+        <v>7020350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,6 +4862,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4898,7 +4893,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700008</v>
+        <v>122700016</v>
       </c>
       <c r="B42" t="n">
         <v>57384</v>
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525081</v>
+        <v>524970</v>
       </c>
       <c r="R42" t="n">
-        <v>7020283</v>
+        <v>7020222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5005,10 +5000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700023</v>
+        <v>122700010</v>
       </c>
       <c r="B43" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,16 +5016,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525274</v>
+        <v>525061</v>
       </c>
       <c r="R43" t="n">
-        <v>7020074</v>
+        <v>7020296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5112,7 +5107,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122699994</v>
+        <v>122699989</v>
       </c>
       <c r="B44" t="n">
         <v>57384</v>
@@ -5152,10 +5147,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524740</v>
+        <v>524846</v>
       </c>
       <c r="R44" t="n">
-        <v>7020346</v>
+        <v>7020185</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5219,7 +5214,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700021</v>
+        <v>122699994</v>
       </c>
       <c r="B45" t="n">
         <v>57384</v>
@@ -5259,10 +5254,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525319</v>
+        <v>524740</v>
       </c>
       <c r="R45" t="n">
-        <v>7020073</v>
+        <v>7020346</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5299,7 +5294,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5326,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700039</v>
+        <v>122700002</v>
       </c>
       <c r="B46" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,21 +5337,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5366,10 +5361,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525354</v>
+        <v>525076</v>
       </c>
       <c r="R46" t="n">
-        <v>7019963</v>
+        <v>7020349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,6 +5397,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700001</v>
+        <v>122700021</v>
       </c>
       <c r="B47" t="n">
         <v>57384</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525052</v>
+        <v>525319</v>
       </c>
       <c r="R47" t="n">
-        <v>7020331</v>
+        <v>7020073</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700037</v>
+        <v>122700018</v>
       </c>
       <c r="B48" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524743</v>
+        <v>525314</v>
       </c>
       <c r="R48" t="n">
-        <v>7020378</v>
+        <v>7020173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,6 +5611,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5637,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122699998</v>
+        <v>122700023</v>
       </c>
       <c r="B49" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5653,16 +5658,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524855</v>
+        <v>525274</v>
       </c>
       <c r="R49" t="n">
-        <v>7020387</v>
+        <v>7020074</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5717,7 +5722,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,7 +5749,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700012</v>
+        <v>122699993</v>
       </c>
       <c r="B50" t="n">
         <v>57384</v>
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524986</v>
+        <v>524750</v>
       </c>
       <c r="R50" t="n">
-        <v>7020251</v>
+        <v>7020358</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5851,7 +5856,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122699993</v>
+        <v>122700000</v>
       </c>
       <c r="B51" t="n">
         <v>57384</v>
@@ -5891,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524750</v>
+        <v>524963</v>
       </c>
       <c r="R51" t="n">
-        <v>7020358</v>
+        <v>7020373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5958,10 +5963,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700004</v>
+        <v>122700028</v>
       </c>
       <c r="B52" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5974,21 +5979,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525112</v>
+        <v>525342</v>
       </c>
       <c r="R52" t="n">
-        <v>7020339</v>
+        <v>7020049</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,11 +6039,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700036</v>
+        <v>122699998</v>
       </c>
       <c r="B31" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524700</v>
+        <v>524855</v>
       </c>
       <c r="R31" t="n">
-        <v>7020267</v>
+        <v>7020387</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3822,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122699998</v>
+        <v>122700033</v>
       </c>
       <c r="B32" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524855</v>
+        <v>525450</v>
       </c>
       <c r="R32" t="n">
-        <v>7020387</v>
+        <v>7019935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,11 +3929,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700033</v>
+        <v>122699990</v>
       </c>
       <c r="B33" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525450</v>
+        <v>524886</v>
       </c>
       <c r="R33" t="n">
-        <v>7019935</v>
+        <v>7020196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,10 +4062,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699990</v>
+        <v>122700037</v>
       </c>
       <c r="B34" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4097,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524886</v>
+        <v>524743</v>
       </c>
       <c r="R34" t="n">
-        <v>7020196</v>
+        <v>7020378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4133,11 +4138,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122700037</v>
+        <v>122700036</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4180,21 +4180,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524743</v>
+        <v>524700</v>
       </c>
       <c r="R35" t="n">
-        <v>7020378</v>
+        <v>7020267</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -2273,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700035</v>
+        <v>122700015</v>
       </c>
       <c r="B17" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525057</v>
+        <v>524981</v>
       </c>
       <c r="R17" t="n">
-        <v>7020101</v>
+        <v>7020235</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,6 +2349,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700015</v>
+        <v>122700035</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524981</v>
+        <v>525057</v>
       </c>
       <c r="R18" t="n">
-        <v>7020235</v>
+        <v>7020101</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,11 +2456,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700009</v>
+        <v>122699987</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525066</v>
+        <v>524637</v>
       </c>
       <c r="R28" t="n">
-        <v>7020292</v>
+        <v>7020366</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700008</v>
+        <v>122700009</v>
       </c>
       <c r="B29" t="n">
         <v>57384</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525081</v>
+        <v>525066</v>
       </c>
       <c r="R29" t="n">
-        <v>7020283</v>
+        <v>7020292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122699987</v>
+        <v>122700008</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524637</v>
+        <v>525081</v>
       </c>
       <c r="R30" t="n">
-        <v>7020366</v>
+        <v>7020283</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122699998</v>
+        <v>122700036</v>
       </c>
       <c r="B31" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524855</v>
+        <v>524700</v>
       </c>
       <c r="R31" t="n">
-        <v>7020387</v>
+        <v>7020267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700033</v>
+        <v>122699998</v>
       </c>
       <c r="B32" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525450</v>
+        <v>524855</v>
       </c>
       <c r="R32" t="n">
-        <v>7019935</v>
+        <v>7020387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,6 +3924,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122699990</v>
+        <v>122700033</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524886</v>
+        <v>525450</v>
       </c>
       <c r="R33" t="n">
-        <v>7020196</v>
+        <v>7019935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,11 +4031,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,10 +4057,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700037</v>
+        <v>122699990</v>
       </c>
       <c r="B34" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4078,21 +4073,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4097,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524743</v>
+        <v>524886</v>
       </c>
       <c r="R34" t="n">
-        <v>7020378</v>
+        <v>7020196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,6 +4133,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122700036</v>
+        <v>122700037</v>
       </c>
       <c r="B35" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4180,21 +4180,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524700</v>
+        <v>524743</v>
       </c>
       <c r="R35" t="n">
-        <v>7020267</v>
+        <v>7020378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -2273,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700015</v>
+        <v>122700035</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524981</v>
+        <v>525057</v>
       </c>
       <c r="R17" t="n">
-        <v>7020235</v>
+        <v>7020101</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,11 +2349,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700035</v>
+        <v>122700015</v>
       </c>
       <c r="B18" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2391,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525057</v>
+        <v>524981</v>
       </c>
       <c r="R18" t="n">
-        <v>7020101</v>
+        <v>7020235</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,6 +2451,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700002</v>
+        <v>122699999</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525076</v>
+        <v>524951</v>
       </c>
       <c r="R6" t="n">
-        <v>7020349</v>
+        <v>7020351</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122699999</v>
+        <v>122700002</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524951</v>
+        <v>525076</v>
       </c>
       <c r="R7" t="n">
-        <v>7020351</v>
+        <v>7020349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700037</v>
+        <v>122700029</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524743</v>
+        <v>525339</v>
       </c>
       <c r="R14" t="n">
-        <v>7020378</v>
+        <v>7020046</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700029</v>
+        <v>122700037</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525339</v>
+        <v>524743</v>
       </c>
       <c r="R15" t="n">
-        <v>7020046</v>
+        <v>7020378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122699989</v>
+        <v>122700017</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524846</v>
+        <v>524976</v>
       </c>
       <c r="R19" t="n">
-        <v>7020185</v>
+        <v>7020218</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700017</v>
+        <v>122699989</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524976</v>
+        <v>524846</v>
       </c>
       <c r="R20" t="n">
-        <v>7020218</v>
+        <v>7020185</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122699993</v>
+        <v>122700033</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>90958</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524750</v>
+        <v>525450</v>
       </c>
       <c r="R28" t="n">
-        <v>7020358</v>
+        <v>7019935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,11 +3508,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122699997</v>
+        <v>122700039</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524808</v>
+        <v>525354</v>
       </c>
       <c r="R29" t="n">
-        <v>7020420</v>
+        <v>7019963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,11 +3610,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700033</v>
+        <v>122700006</v>
       </c>
       <c r="B30" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525450</v>
+        <v>525089</v>
       </c>
       <c r="R30" t="n">
-        <v>7019935</v>
+        <v>7020329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,6 +3712,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700039</v>
+        <v>122699993</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525354</v>
+        <v>524750</v>
       </c>
       <c r="R31" t="n">
-        <v>7019963</v>
+        <v>7020358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3819,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700006</v>
+        <v>122699997</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525089</v>
+        <v>524808</v>
       </c>
       <c r="R32" t="n">
-        <v>7020329</v>
+        <v>7020420</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122700013</v>
+        <v>122699996</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524981</v>
+        <v>524805</v>
       </c>
       <c r="R35" t="n">
-        <v>7020231</v>
+        <v>7020421</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700003</v>
+        <v>122700022</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90951</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4285,25 +4285,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525101</v>
+        <v>525086</v>
       </c>
       <c r="R36" t="n">
-        <v>7020350</v>
+        <v>7019775</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4349,11 +4349,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,7 +4375,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122699996</v>
+        <v>122700013</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4420,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524805</v>
+        <v>524981</v>
       </c>
       <c r="R37" t="n">
-        <v>7020421</v>
+        <v>7020231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700022</v>
+        <v>122700003</v>
       </c>
       <c r="B38" t="n">
-        <v>90951</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,25 +4494,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4527,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525086</v>
+        <v>525101</v>
       </c>
       <c r="R38" t="n">
-        <v>7019775</v>
+        <v>7020350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4563,6 +4558,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700008</v>
+        <v>122700030</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525081</v>
+        <v>524857</v>
       </c>
       <c r="R2" t="n">
-        <v>7020283</v>
+        <v>7020120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700007</v>
+        <v>122700023</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525106</v>
+        <v>525274</v>
       </c>
       <c r="R3" t="n">
-        <v>7020311</v>
+        <v>7020074</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122699995</v>
+        <v>122700035</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524719</v>
+        <v>525057</v>
       </c>
       <c r="R4" t="n">
-        <v>7020350</v>
+        <v>7020101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700005</v>
+        <v>122699999</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525103</v>
+        <v>524951</v>
       </c>
       <c r="R5" t="n">
-        <v>7020335</v>
+        <v>7020351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122699999</v>
+        <v>122699995</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524951</v>
+        <v>524719</v>
       </c>
       <c r="R6" t="n">
-        <v>7020351</v>
+        <v>7020350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700002</v>
+        <v>122700018</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525076</v>
+        <v>525314</v>
       </c>
       <c r="R7" t="n">
-        <v>7020349</v>
+        <v>7020173</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700026</v>
+        <v>122700006</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525299</v>
+        <v>525089</v>
       </c>
       <c r="R8" t="n">
-        <v>7019885</v>
+        <v>7020329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700020</v>
+        <v>122700012</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525498</v>
+        <v>524986</v>
       </c>
       <c r="R9" t="n">
-        <v>7020014</v>
+        <v>7020251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700036</v>
+        <v>122700021</v>
       </c>
       <c r="B10" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524700</v>
+        <v>525319</v>
       </c>
       <c r="R10" t="n">
-        <v>7020267</v>
+        <v>7020073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122699994</v>
+        <v>122699991</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524740</v>
+        <v>524850</v>
       </c>
       <c r="R11" t="n">
-        <v>7020346</v>
+        <v>7020302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700004</v>
+        <v>122700037</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525112</v>
+        <v>524743</v>
       </c>
       <c r="R12" t="n">
-        <v>7020339</v>
+        <v>7020378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700012</v>
+        <v>122700034</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524986</v>
+        <v>525015</v>
       </c>
       <c r="R13" t="n">
-        <v>7020251</v>
+        <v>7019776</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700029</v>
+        <v>122700003</v>
       </c>
       <c r="B14" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525339</v>
+        <v>525101</v>
       </c>
       <c r="R14" t="n">
-        <v>7020046</v>
+        <v>7020350</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700037</v>
+        <v>122700001</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524743</v>
+        <v>525052</v>
       </c>
       <c r="R15" t="n">
-        <v>7020378</v>
+        <v>7020331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122699998</v>
+        <v>122699992</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524855</v>
+        <v>524791</v>
       </c>
       <c r="R16" t="n">
-        <v>7020387</v>
+        <v>7020365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700032</v>
+        <v>122700002</v>
       </c>
       <c r="B17" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525024</v>
+        <v>525076</v>
       </c>
       <c r="R17" t="n">
-        <v>7020263</v>
+        <v>7020349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700023</v>
+        <v>122700031</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525274</v>
+        <v>524640</v>
       </c>
       <c r="R18" t="n">
-        <v>7020074</v>
+        <v>7020358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,11 +2443,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700017</v>
+        <v>122700027</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524976</v>
+        <v>525364</v>
       </c>
       <c r="R19" t="n">
-        <v>7020218</v>
+        <v>7020041</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122699989</v>
+        <v>122700014</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2616,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524846</v>
+        <v>524981</v>
       </c>
       <c r="R20" t="n">
-        <v>7020185</v>
+        <v>7020235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700021</v>
+        <v>122700033</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525319</v>
+        <v>525450</v>
       </c>
       <c r="R21" t="n">
-        <v>7020073</v>
+        <v>7019935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700010</v>
+        <v>122699990</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2830,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525061</v>
+        <v>524886</v>
       </c>
       <c r="R22" t="n">
-        <v>7020296</v>
+        <v>7020196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700019</v>
+        <v>122700029</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525451</v>
+        <v>525339</v>
       </c>
       <c r="R23" t="n">
-        <v>7020169</v>
+        <v>7020046</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,11 +2963,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700018</v>
+        <v>122700028</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525314</v>
+        <v>525342</v>
       </c>
       <c r="R24" t="n">
-        <v>7020173</v>
+        <v>7020049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3080,11 +3065,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,7 +3091,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700016</v>
+        <v>122700009</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3151,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524970</v>
+        <v>525066</v>
       </c>
       <c r="R25" t="n">
-        <v>7020222</v>
+        <v>7020292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,7 +3198,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700001</v>
+        <v>122700010</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3258,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525052</v>
+        <v>525061</v>
       </c>
       <c r="R26" t="n">
-        <v>7020331</v>
+        <v>7020296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3305,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122699992</v>
+        <v>122700000</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3365,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524791</v>
+        <v>524963</v>
       </c>
       <c r="R27" t="n">
-        <v>7020365</v>
+        <v>7020373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700033</v>
+        <v>122700020</v>
       </c>
       <c r="B28" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3472,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525450</v>
+        <v>525498</v>
       </c>
       <c r="R28" t="n">
-        <v>7019935</v>
+        <v>7020014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,6 +3488,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700039</v>
+        <v>122700019</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525354</v>
+        <v>525451</v>
       </c>
       <c r="R29" t="n">
-        <v>7019963</v>
+        <v>7020169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,6 +3595,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3636,7 +3626,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700006</v>
+        <v>122699998</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3676,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525089</v>
+        <v>524855</v>
       </c>
       <c r="R30" t="n">
-        <v>7020329</v>
+        <v>7020387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122699993</v>
+        <v>122700008</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3783,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524750</v>
+        <v>525081</v>
       </c>
       <c r="R31" t="n">
-        <v>7020358</v>
+        <v>7020283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,7 +3840,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122699997</v>
+        <v>122700013</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3890,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524808</v>
+        <v>524981</v>
       </c>
       <c r="R32" t="n">
-        <v>7020420</v>
+        <v>7020231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,7 +3947,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122699990</v>
+        <v>122700016</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3997,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524886</v>
+        <v>524970</v>
       </c>
       <c r="R33" t="n">
-        <v>7020196</v>
+        <v>7020222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700034</v>
+        <v>122699988</v>
       </c>
       <c r="B34" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4070,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525015</v>
+        <v>524640</v>
       </c>
       <c r="R34" t="n">
-        <v>7019776</v>
+        <v>7020358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4130,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,7 +4161,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699996</v>
+        <v>122699997</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524805</v>
+        <v>524808</v>
       </c>
       <c r="R35" t="n">
-        <v>7020421</v>
+        <v>7020420</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4273,10 +4268,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700022</v>
+        <v>122699996</v>
       </c>
       <c r="B36" t="n">
-        <v>90951</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4285,25 +4280,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4313,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525086</v>
+        <v>524805</v>
       </c>
       <c r="R36" t="n">
-        <v>7019775</v>
+        <v>7020421</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4349,6 +4344,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4375,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700013</v>
+        <v>122700007</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524981</v>
+        <v>525106</v>
       </c>
       <c r="R37" t="n">
-        <v>7020231</v>
+        <v>7020311</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4482,7 +4482,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700003</v>
+        <v>122699987</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525101</v>
+        <v>524637</v>
       </c>
       <c r="R38" t="n">
-        <v>7020350</v>
+        <v>7020366</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700027</v>
+        <v>122700039</v>
       </c>
       <c r="B39" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525364</v>
+        <v>525354</v>
       </c>
       <c r="R39" t="n">
-        <v>7020041</v>
+        <v>7019963</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700015</v>
+        <v>122700032</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524981</v>
+        <v>525024</v>
       </c>
       <c r="R40" t="n">
-        <v>7020235</v>
+        <v>7020263</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,11 +4767,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4798,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700025</v>
+        <v>122700026</v>
       </c>
       <c r="B41" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4838,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525407</v>
+        <v>525299</v>
       </c>
       <c r="R41" t="n">
-        <v>7020146</v>
+        <v>7019885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4900,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700028</v>
+        <v>122699994</v>
       </c>
       <c r="B42" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,21 +4911,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4935,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525342</v>
+        <v>524740</v>
       </c>
       <c r="R42" t="n">
-        <v>7020049</v>
+        <v>7020346</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4976,6 +4971,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700031</v>
+        <v>122699989</v>
       </c>
       <c r="B43" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524640</v>
+        <v>524846</v>
       </c>
       <c r="R43" t="n">
-        <v>7020358</v>
+        <v>7020185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,6 +5078,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5104,10 +5109,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700024</v>
+        <v>122700022</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>90955</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5116,25 +5121,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5144,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524639</v>
+        <v>525086</v>
       </c>
       <c r="R44" t="n">
-        <v>7020328</v>
+        <v>7019775</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,11 +5185,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5211,7 +5211,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122699986</v>
+        <v>122700005</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5245,24 +5245,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525217</v>
+        <v>525103</v>
       </c>
       <c r="R45" t="n">
-        <v>7020178</v>
+        <v>7020335</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5299,7 +5291,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5326,7 +5318,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122699987</v>
+        <v>122700017</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5366,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524637</v>
+        <v>524976</v>
       </c>
       <c r="R46" t="n">
-        <v>7020366</v>
+        <v>7020218</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5406,7 +5398,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5433,10 +5425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700030</v>
+        <v>122699993</v>
       </c>
       <c r="B47" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5449,21 +5441,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5465,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524857</v>
+        <v>524750</v>
       </c>
       <c r="R47" t="n">
-        <v>7020120</v>
+        <v>7020358</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5509,6 +5501,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5535,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700035</v>
+        <v>122699986</v>
       </c>
       <c r="B48" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5551,34 +5548,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525057</v>
+        <v>525217</v>
       </c>
       <c r="R48" t="n">
-        <v>7020101</v>
+        <v>7020178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,6 +5616,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5637,10 +5647,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122699988</v>
+        <v>122700036</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5653,21 +5663,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5677,10 +5687,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524640</v>
+        <v>524700</v>
       </c>
       <c r="R49" t="n">
-        <v>7020358</v>
+        <v>7020267</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5713,11 +5723,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,10 +5749,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700000</v>
+        <v>122700024</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5760,16 +5765,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524963</v>
+        <v>524639</v>
       </c>
       <c r="R50" t="n">
-        <v>7020373</v>
+        <v>7020328</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5824,7 +5829,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5851,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122699991</v>
+        <v>122700025</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,21 +5872,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5891,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524850</v>
+        <v>525407</v>
       </c>
       <c r="R51" t="n">
-        <v>7020302</v>
+        <v>7020146</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5927,11 +5932,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700009</v>
+        <v>122700004</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525066</v>
+        <v>525112</v>
       </c>
       <c r="R52" t="n">
-        <v>7020292</v>
+        <v>7020339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700018</v>
+        <v>122699991</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525314</v>
+        <v>524850</v>
       </c>
       <c r="R7" t="n">
-        <v>7020173</v>
+        <v>7020302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700006</v>
+        <v>122700018</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525089</v>
+        <v>525314</v>
       </c>
       <c r="R8" t="n">
-        <v>7020329</v>
+        <v>7020173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700012</v>
+        <v>122700006</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524986</v>
+        <v>525089</v>
       </c>
       <c r="R9" t="n">
-        <v>7020251</v>
+        <v>7020329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700021</v>
+        <v>122700012</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525319</v>
+        <v>524986</v>
       </c>
       <c r="R10" t="n">
-        <v>7020073</v>
+        <v>7020251</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122699991</v>
+        <v>122700021</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524850</v>
+        <v>525319</v>
       </c>
       <c r="R11" t="n">
-        <v>7020302</v>
+        <v>7020073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700037</v>
+        <v>122700034</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524743</v>
+        <v>525015</v>
       </c>
       <c r="R12" t="n">
-        <v>7020378</v>
+        <v>7019776</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700034</v>
+        <v>122700037</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525015</v>
+        <v>524743</v>
       </c>
       <c r="R13" t="n">
-        <v>7019776</v>
+        <v>7020378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700039</v>
+        <v>122700032</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525354</v>
+        <v>525024</v>
       </c>
       <c r="R39" t="n">
-        <v>7019963</v>
+        <v>7020263</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700032</v>
+        <v>122700026</v>
       </c>
       <c r="B40" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525024</v>
+        <v>525299</v>
       </c>
       <c r="R40" t="n">
-        <v>7020263</v>
+        <v>7019885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700026</v>
+        <v>122699994</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525299</v>
+        <v>524740</v>
       </c>
       <c r="R41" t="n">
-        <v>7019885</v>
+        <v>7020346</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,6 +4869,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,7 +4900,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122699994</v>
+        <v>122699989</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4935,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524740</v>
+        <v>524846</v>
       </c>
       <c r="R42" t="n">
-        <v>7020346</v>
+        <v>7020185</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5002,10 +5007,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122699989</v>
+        <v>122700039</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,21 +5023,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524846</v>
+        <v>525354</v>
       </c>
       <c r="R43" t="n">
-        <v>7020185</v>
+        <v>7019963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,11 +5083,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700023</v>
+        <v>122700026</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525274</v>
+        <v>525299</v>
       </c>
       <c r="R3" t="n">
-        <v>7020074</v>
+        <v>7019885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700035</v>
+        <v>122700017</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525057</v>
+        <v>524976</v>
       </c>
       <c r="R4" t="n">
-        <v>7020101</v>
+        <v>7020218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122699999</v>
+        <v>122700039</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524951</v>
+        <v>525354</v>
       </c>
       <c r="R5" t="n">
-        <v>7020351</v>
+        <v>7019963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122699995</v>
+        <v>122700029</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524719</v>
+        <v>525339</v>
       </c>
       <c r="R6" t="n">
-        <v>7020350</v>
+        <v>7020046</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122699991</v>
+        <v>122700005</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524850</v>
+        <v>525103</v>
       </c>
       <c r="R7" t="n">
-        <v>7020302</v>
+        <v>7020335</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700018</v>
+        <v>122700002</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525314</v>
+        <v>525076</v>
       </c>
       <c r="R8" t="n">
-        <v>7020173</v>
+        <v>7020349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700006</v>
+        <v>122700015</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525089</v>
+        <v>524981</v>
       </c>
       <c r="R9" t="n">
-        <v>7020329</v>
+        <v>7020235</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700012</v>
+        <v>122699990</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524986</v>
+        <v>524886</v>
       </c>
       <c r="R10" t="n">
-        <v>7020251</v>
+        <v>7020196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700021</v>
+        <v>122699994</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525319</v>
+        <v>524740</v>
       </c>
       <c r="R11" t="n">
-        <v>7020073</v>
+        <v>7020346</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700034</v>
+        <v>122700001</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525015</v>
+        <v>525052</v>
       </c>
       <c r="R12" t="n">
-        <v>7019776</v>
+        <v>7020331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700037</v>
+        <v>122699992</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524743</v>
+        <v>524791</v>
       </c>
       <c r="R13" t="n">
-        <v>7020378</v>
+        <v>7020365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700003</v>
+        <v>122700023</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525101</v>
+        <v>525274</v>
       </c>
       <c r="R14" t="n">
-        <v>7020350</v>
+        <v>7020074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700001</v>
+        <v>122700027</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525052</v>
+        <v>525364</v>
       </c>
       <c r="R15" t="n">
-        <v>7020331</v>
+        <v>7020041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122699992</v>
+        <v>122699987</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524791</v>
+        <v>524637</v>
       </c>
       <c r="R16" t="n">
-        <v>7020365</v>
+        <v>7020366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700002</v>
+        <v>122700033</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525076</v>
+        <v>525450</v>
       </c>
       <c r="R17" t="n">
-        <v>7020349</v>
+        <v>7019935</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700031</v>
+        <v>122700037</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524640</v>
+        <v>524743</v>
       </c>
       <c r="R18" t="n">
-        <v>7020358</v>
+        <v>7020378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700027</v>
+        <v>122700004</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525364</v>
+        <v>525112</v>
       </c>
       <c r="R19" t="n">
-        <v>7020041</v>
+        <v>7020339</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2535,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700014</v>
+        <v>122700028</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524981</v>
+        <v>525342</v>
       </c>
       <c r="R20" t="n">
-        <v>7020235</v>
+        <v>7020049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,11 +2642,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700033</v>
+        <v>122700018</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525450</v>
+        <v>525314</v>
       </c>
       <c r="R21" t="n">
-        <v>7019935</v>
+        <v>7020173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122699990</v>
+        <v>122699997</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2820,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524886</v>
+        <v>524808</v>
       </c>
       <c r="R22" t="n">
-        <v>7020196</v>
+        <v>7020420</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700029</v>
+        <v>122699991</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525339</v>
+        <v>524850</v>
       </c>
       <c r="R23" t="n">
-        <v>7020046</v>
+        <v>7020302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,6 +2958,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700028</v>
+        <v>122699996</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525342</v>
+        <v>524805</v>
       </c>
       <c r="R24" t="n">
-        <v>7020049</v>
+        <v>7020421</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,6 +3065,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700010</v>
+        <v>122699993</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3238,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525061</v>
+        <v>524750</v>
       </c>
       <c r="R26" t="n">
-        <v>7020296</v>
+        <v>7020358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,7 +3310,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700000</v>
+        <v>122699999</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524963</v>
+        <v>524951</v>
       </c>
       <c r="R27" t="n">
-        <v>7020373</v>
+        <v>7020351</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,7 +3417,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700020</v>
+        <v>122700021</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3452,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525498</v>
+        <v>525319</v>
       </c>
       <c r="R28" t="n">
-        <v>7020014</v>
+        <v>7020073</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3497,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700019</v>
+        <v>122700025</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525451</v>
+        <v>525407</v>
       </c>
       <c r="R29" t="n">
-        <v>7020169</v>
+        <v>7020146</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,11 +3600,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122699998</v>
+        <v>122700024</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,16 +3642,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524855</v>
+        <v>524639</v>
       </c>
       <c r="R30" t="n">
-        <v>7020387</v>
+        <v>7020328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700008</v>
+        <v>122700007</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525081</v>
+        <v>525106</v>
       </c>
       <c r="R31" t="n">
-        <v>7020283</v>
+        <v>7020311</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,7 +3840,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700013</v>
+        <v>122700012</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524981</v>
+        <v>524986</v>
       </c>
       <c r="R32" t="n">
-        <v>7020231</v>
+        <v>7020251</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700016</v>
+        <v>122700034</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3963,21 +3963,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524970</v>
+        <v>525015</v>
       </c>
       <c r="R33" t="n">
-        <v>7020222</v>
+        <v>7019776</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,11 +4023,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4054,7 +4049,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699988</v>
+        <v>122700003</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4094,10 +4089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524640</v>
+        <v>525101</v>
       </c>
       <c r="R34" t="n">
-        <v>7020358</v>
+        <v>7020350</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4134,7 +4129,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4161,7 +4156,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699997</v>
+        <v>122699986</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4195,16 +4190,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524808</v>
+        <v>525217</v>
       </c>
       <c r="R35" t="n">
-        <v>7020420</v>
+        <v>7020178</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4244,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,10 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122699996</v>
+        <v>122700036</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4284,21 +4287,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4308,10 +4311,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524805</v>
+        <v>524700</v>
       </c>
       <c r="R36" t="n">
-        <v>7020421</v>
+        <v>7020267</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,11 +4347,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4373,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700007</v>
+        <v>122700016</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4415,10 +4413,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525106</v>
+        <v>524970</v>
       </c>
       <c r="R37" t="n">
-        <v>7020311</v>
+        <v>7020222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,7 +4453,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4482,7 +4480,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122699987</v>
+        <v>122700000</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4522,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524637</v>
+        <v>524963</v>
       </c>
       <c r="R38" t="n">
-        <v>7020366</v>
+        <v>7020373</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4562,7 +4560,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4589,10 +4587,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700032</v>
+        <v>122700022</v>
       </c>
       <c r="B39" t="n">
-        <v>90962</v>
+        <v>90955</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,25 +4599,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4629,10 +4627,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525024</v>
+        <v>525086</v>
       </c>
       <c r="R39" t="n">
-        <v>7020263</v>
+        <v>7019775</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700026</v>
+        <v>122700010</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4707,21 +4705,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525299</v>
+        <v>525061</v>
       </c>
       <c r="R40" t="n">
-        <v>7019885</v>
+        <v>7020296</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,6 +4765,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4793,7 +4796,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122699994</v>
+        <v>122699989</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -4833,10 +4836,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524740</v>
+        <v>524846</v>
       </c>
       <c r="R41" t="n">
-        <v>7020346</v>
+        <v>7020185</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4900,7 +4903,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122699989</v>
+        <v>122699988</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4940,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524846</v>
+        <v>524640</v>
       </c>
       <c r="R42" t="n">
-        <v>7020185</v>
+        <v>7020358</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,10 +5010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700039</v>
+        <v>122700035</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5023,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5047,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525354</v>
+        <v>525057</v>
       </c>
       <c r="R43" t="n">
-        <v>7019963</v>
+        <v>7020101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5109,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700022</v>
+        <v>122700032</v>
       </c>
       <c r="B44" t="n">
-        <v>90955</v>
+        <v>90962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5121,25 +5124,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5152,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525086</v>
+        <v>525024</v>
       </c>
       <c r="R44" t="n">
-        <v>7019775</v>
+        <v>7020263</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700005</v>
+        <v>122700020</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5251,10 +5254,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525103</v>
+        <v>525498</v>
       </c>
       <c r="R45" t="n">
-        <v>7020335</v>
+        <v>7020014</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5291,7 +5294,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,7 +5321,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700017</v>
+        <v>122700006</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5358,10 +5361,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524976</v>
+        <v>525089</v>
       </c>
       <c r="R46" t="n">
-        <v>7020218</v>
+        <v>7020329</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5425,7 +5428,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122699993</v>
+        <v>122700019</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5465,10 +5468,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524750</v>
+        <v>525451</v>
       </c>
       <c r="R47" t="n">
-        <v>7020358</v>
+        <v>7020169</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122699986</v>
+        <v>122699998</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5566,24 +5569,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525217</v>
+        <v>524855</v>
       </c>
       <c r="R48" t="n">
-        <v>7020178</v>
+        <v>7020387</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5620,7 +5615,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5647,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700036</v>
+        <v>122699995</v>
       </c>
       <c r="B49" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,21 +5658,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524700</v>
+        <v>524719</v>
       </c>
       <c r="R49" t="n">
-        <v>7020267</v>
+        <v>7020350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,6 +5718,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700024</v>
+        <v>122700008</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5765,16 +5765,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524639</v>
+        <v>525081</v>
       </c>
       <c r="R50" t="n">
-        <v>7020328</v>
+        <v>7020283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700025</v>
+        <v>122700013</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,21 +5872,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525407</v>
+        <v>524981</v>
       </c>
       <c r="R51" t="n">
-        <v>7020146</v>
+        <v>7020231</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5932,6 +5932,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,10 +5963,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700004</v>
+        <v>122700031</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5974,21 +5979,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525112</v>
+        <v>524640</v>
       </c>
       <c r="R52" t="n">
-        <v>7020339</v>
+        <v>7020358</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,11 +6039,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700030</v>
+        <v>122700009</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524857</v>
+        <v>525066</v>
       </c>
       <c r="R2" t="n">
-        <v>7020120</v>
+        <v>7020292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700026</v>
+        <v>122699998</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525299</v>
+        <v>524855</v>
       </c>
       <c r="R3" t="n">
-        <v>7019885</v>
+        <v>7020387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700017</v>
+        <v>122700034</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524976</v>
+        <v>525015</v>
       </c>
       <c r="R4" t="n">
-        <v>7020218</v>
+        <v>7019776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700039</v>
+        <v>122700002</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525354</v>
+        <v>525076</v>
       </c>
       <c r="R5" t="n">
-        <v>7019963</v>
+        <v>7020349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700029</v>
+        <v>122700017</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525339</v>
+        <v>524976</v>
       </c>
       <c r="R6" t="n">
-        <v>7020046</v>
+        <v>7020218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700005</v>
+        <v>122700039</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525103</v>
+        <v>525354</v>
       </c>
       <c r="R7" t="n">
-        <v>7020335</v>
+        <v>7019963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700002</v>
+        <v>122699993</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1337,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525076</v>
+        <v>524750</v>
       </c>
       <c r="R8" t="n">
-        <v>7020349</v>
+        <v>7020358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700015</v>
+        <v>122700004</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524981</v>
+        <v>525112</v>
       </c>
       <c r="R9" t="n">
-        <v>7020235</v>
+        <v>7020339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122699990</v>
+        <v>122700016</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524886</v>
+        <v>524970</v>
       </c>
       <c r="R10" t="n">
-        <v>7020196</v>
+        <v>7020222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122699994</v>
+        <v>122700000</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1658,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524740</v>
+        <v>524963</v>
       </c>
       <c r="R11" t="n">
-        <v>7020346</v>
+        <v>7020373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700001</v>
+        <v>122699997</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1765,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525052</v>
+        <v>524808</v>
       </c>
       <c r="R12" t="n">
-        <v>7020331</v>
+        <v>7020420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122699992</v>
+        <v>122699995</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524791</v>
+        <v>524719</v>
       </c>
       <c r="R13" t="n">
-        <v>7020365</v>
+        <v>7020350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700027</v>
+        <v>122700020</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525364</v>
+        <v>525498</v>
       </c>
       <c r="R15" t="n">
-        <v>7020041</v>
+        <v>7020014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122699987</v>
+        <v>122700010</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2188,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524637</v>
+        <v>525061</v>
       </c>
       <c r="R16" t="n">
-        <v>7020366</v>
+        <v>7020296</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700033</v>
+        <v>122700035</v>
       </c>
       <c r="B17" t="n">
         <v>90962</v>
@@ -2295,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525450</v>
+        <v>525057</v>
       </c>
       <c r="R17" t="n">
-        <v>7019935</v>
+        <v>7020101</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700037</v>
+        <v>122700003</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524743</v>
+        <v>525101</v>
       </c>
       <c r="R18" t="n">
-        <v>7020378</v>
+        <v>7020350</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700004</v>
+        <v>122699994</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2499,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525112</v>
+        <v>524740</v>
       </c>
       <c r="R19" t="n">
-        <v>7020339</v>
+        <v>7020346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700028</v>
+        <v>122699990</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525342</v>
+        <v>524886</v>
       </c>
       <c r="R20" t="n">
-        <v>7020049</v>
+        <v>7020196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700018</v>
+        <v>122699996</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2708,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525314</v>
+        <v>524805</v>
       </c>
       <c r="R21" t="n">
-        <v>7020173</v>
+        <v>7020421</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122699997</v>
+        <v>122700031</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524808</v>
+        <v>524640</v>
       </c>
       <c r="R22" t="n">
-        <v>7020420</v>
+        <v>7020358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,11 +2876,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122699991</v>
+        <v>122700012</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2922,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524850</v>
+        <v>524986</v>
       </c>
       <c r="R23" t="n">
-        <v>7020302</v>
+        <v>7020251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122699996</v>
+        <v>122700006</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3029,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524805</v>
+        <v>525089</v>
       </c>
       <c r="R24" t="n">
-        <v>7020421</v>
+        <v>7020329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700009</v>
+        <v>122699989</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3136,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525066</v>
+        <v>524846</v>
       </c>
       <c r="R25" t="n">
-        <v>7020292</v>
+        <v>7020185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122699993</v>
+        <v>122700024</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,16 +3239,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3243,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524750</v>
+        <v>524639</v>
       </c>
       <c r="R26" t="n">
-        <v>7020358</v>
+        <v>7020328</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122699999</v>
+        <v>122700022</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524951</v>
+        <v>525086</v>
       </c>
       <c r="R27" t="n">
-        <v>7020351</v>
+        <v>7019775</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700021</v>
+        <v>122700037</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3448,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525319</v>
+        <v>524743</v>
       </c>
       <c r="R28" t="n">
-        <v>7020073</v>
+        <v>7020378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,11 +3508,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700025</v>
+        <v>122700019</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3564,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525407</v>
+        <v>525451</v>
       </c>
       <c r="R29" t="n">
-        <v>7020146</v>
+        <v>7020169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700024</v>
+        <v>122700013</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,16 +3657,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3666,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524639</v>
+        <v>524981</v>
       </c>
       <c r="R30" t="n">
-        <v>7020328</v>
+        <v>7020231</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700007</v>
+        <v>122700014</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3773,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525106</v>
+        <v>524981</v>
       </c>
       <c r="R31" t="n">
-        <v>7020311</v>
+        <v>7020235</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700012</v>
+        <v>122700001</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3880,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524986</v>
+        <v>525052</v>
       </c>
       <c r="R32" t="n">
-        <v>7020251</v>
+        <v>7020331</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700034</v>
+        <v>122700033</v>
       </c>
       <c r="B33" t="n">
         <v>90962</v>
@@ -3987,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525015</v>
+        <v>525450</v>
       </c>
       <c r="R33" t="n">
-        <v>7019776</v>
+        <v>7019935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700003</v>
+        <v>122700029</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525101</v>
+        <v>525339</v>
       </c>
       <c r="R34" t="n">
-        <v>7020350</v>
+        <v>7020046</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,11 +4140,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4271,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700036</v>
+        <v>122699992</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4287,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4311,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524700</v>
+        <v>524791</v>
       </c>
       <c r="R36" t="n">
-        <v>7020267</v>
+        <v>7020365</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4347,6 +4357,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4373,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700016</v>
+        <v>122700025</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4389,21 +4404,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4413,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524970</v>
+        <v>525407</v>
       </c>
       <c r="R37" t="n">
-        <v>7020222</v>
+        <v>7020146</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,11 +4464,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4480,7 +4490,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700000</v>
+        <v>122700008</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4520,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524963</v>
+        <v>525081</v>
       </c>
       <c r="R38" t="n">
-        <v>7020373</v>
+        <v>7020283</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700022</v>
+        <v>122700032</v>
       </c>
       <c r="B39" t="n">
-        <v>90955</v>
+        <v>90962</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4599,25 +4609,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4627,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525086</v>
+        <v>525024</v>
       </c>
       <c r="R39" t="n">
-        <v>7019775</v>
+        <v>7020263</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700010</v>
+        <v>122700036</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,21 +4715,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4729,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525061</v>
+        <v>524700</v>
       </c>
       <c r="R40" t="n">
-        <v>7020296</v>
+        <v>7020267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4765,11 +4775,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4796,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122699989</v>
+        <v>122700026</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4812,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4836,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524846</v>
+        <v>525299</v>
       </c>
       <c r="R41" t="n">
-        <v>7020185</v>
+        <v>7019885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,11 +4877,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700035</v>
+        <v>122700030</v>
       </c>
       <c r="B43" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525057</v>
+        <v>524857</v>
       </c>
       <c r="R43" t="n">
-        <v>7020101</v>
+        <v>7020120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700032</v>
+        <v>122699987</v>
       </c>
       <c r="B44" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5128,21 +5128,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525024</v>
+        <v>524637</v>
       </c>
       <c r="R44" t="n">
-        <v>7020263</v>
+        <v>7020366</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5188,6 +5188,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5214,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700020</v>
+        <v>122700027</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5230,21 +5235,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5254,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525498</v>
+        <v>525364</v>
       </c>
       <c r="R45" t="n">
-        <v>7020014</v>
+        <v>7020041</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5290,11 +5295,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5321,7 +5321,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700006</v>
+        <v>122700018</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525089</v>
+        <v>525314</v>
       </c>
       <c r="R46" t="n">
-        <v>7020329</v>
+        <v>7020173</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700019</v>
+        <v>122699999</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525451</v>
+        <v>524951</v>
       </c>
       <c r="R47" t="n">
-        <v>7020169</v>
+        <v>7020351</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122699998</v>
+        <v>122700028</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524855</v>
+        <v>525342</v>
       </c>
       <c r="R48" t="n">
-        <v>7020387</v>
+        <v>7020049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,11 +5611,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5642,7 +5637,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122699995</v>
+        <v>122700005</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5682,10 +5677,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524719</v>
+        <v>525103</v>
       </c>
       <c r="R49" t="n">
-        <v>7020350</v>
+        <v>7020335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5749,7 +5744,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700008</v>
+        <v>122699991</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -5789,10 +5784,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525081</v>
+        <v>524850</v>
       </c>
       <c r="R50" t="n">
-        <v>7020283</v>
+        <v>7020302</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5829,7 +5824,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,7 +5851,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700013</v>
+        <v>122700007</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -5896,10 +5891,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524981</v>
+        <v>525106</v>
       </c>
       <c r="R51" t="n">
-        <v>7020231</v>
+        <v>7020311</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5936,7 +5931,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5963,10 +5958,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700031</v>
+        <v>122700021</v>
       </c>
       <c r="B52" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5979,21 +5974,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6003,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524640</v>
+        <v>525319</v>
       </c>
       <c r="R52" t="n">
-        <v>7020358</v>
+        <v>7020073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6039,6 +6034,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122699995</v>
+        <v>122700020</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524719</v>
+        <v>525498</v>
       </c>
       <c r="R13" t="n">
-        <v>7020350</v>
+        <v>7020014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700023</v>
+        <v>122700010</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525274</v>
+        <v>525061</v>
       </c>
       <c r="R14" t="n">
-        <v>7020074</v>
+        <v>7020296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700020</v>
+        <v>122699995</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525498</v>
+        <v>524719</v>
       </c>
       <c r="R15" t="n">
-        <v>7020014</v>
+        <v>7020350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700010</v>
+        <v>122700023</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525061</v>
+        <v>525274</v>
       </c>
       <c r="R16" t="n">
-        <v>7020296</v>
+        <v>7020074</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700035</v>
+        <v>122699994</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525057</v>
+        <v>524740</v>
       </c>
       <c r="R17" t="n">
-        <v>7020101</v>
+        <v>7020346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700003</v>
+        <v>122700035</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525101</v>
+        <v>525057</v>
       </c>
       <c r="R18" t="n">
-        <v>7020350</v>
+        <v>7020101</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122699994</v>
+        <v>122700003</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524740</v>
+        <v>525101</v>
       </c>
       <c r="R19" t="n">
-        <v>7020346</v>
+        <v>7020350</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700001</v>
+        <v>122700033</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525052</v>
+        <v>525450</v>
       </c>
       <c r="R32" t="n">
-        <v>7020331</v>
+        <v>7019935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,11 +3931,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700033</v>
+        <v>122700001</v>
       </c>
       <c r="B33" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525450</v>
+        <v>525052</v>
       </c>
       <c r="R33" t="n">
-        <v>7019935</v>
+        <v>7020331</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4033,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700029</v>
+        <v>122699986</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,34 +4080,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525339</v>
+        <v>525217</v>
       </c>
       <c r="R34" t="n">
-        <v>7020046</v>
+        <v>7020178</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4148,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,7 +4179,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699986</v>
+        <v>122699992</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4200,24 +4213,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525217</v>
+        <v>524791</v>
       </c>
       <c r="R35" t="n">
-        <v>7020178</v>
+        <v>7020365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,7 +4259,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122699992</v>
+        <v>122700029</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4302,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4321,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524791</v>
+        <v>525339</v>
       </c>
       <c r="R36" t="n">
-        <v>7020365</v>
+        <v>7020046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,11 +4362,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122699987</v>
+        <v>122700018</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524637</v>
+        <v>525314</v>
       </c>
       <c r="R44" t="n">
-        <v>7020366</v>
+        <v>7020173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700027</v>
+        <v>122699987</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525364</v>
+        <v>524637</v>
       </c>
       <c r="R45" t="n">
-        <v>7020041</v>
+        <v>7020366</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,6 +5295,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5321,10 +5326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700018</v>
+        <v>122700027</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5337,21 +5342,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5361,10 +5366,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525314</v>
+        <v>525364</v>
       </c>
       <c r="R46" t="n">
-        <v>7020173</v>
+        <v>7020041</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5397,11 +5402,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700017</v>
+        <v>122700039</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524976</v>
+        <v>525354</v>
       </c>
       <c r="R6" t="n">
-        <v>7020218</v>
+        <v>7019963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700039</v>
+        <v>122700017</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525354</v>
+        <v>524976</v>
       </c>
       <c r="R7" t="n">
-        <v>7019963</v>
+        <v>7020218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700020</v>
+        <v>122699995</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525498</v>
+        <v>524719</v>
       </c>
       <c r="R13" t="n">
-        <v>7020014</v>
+        <v>7020350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700010</v>
+        <v>122700023</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525061</v>
+        <v>525274</v>
       </c>
       <c r="R14" t="n">
-        <v>7020296</v>
+        <v>7020074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122699995</v>
+        <v>122700020</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524719</v>
+        <v>525498</v>
       </c>
       <c r="R15" t="n">
-        <v>7020350</v>
+        <v>7020014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700023</v>
+        <v>122700010</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525274</v>
+        <v>525061</v>
       </c>
       <c r="R16" t="n">
-        <v>7020074</v>
+        <v>7020296</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700018</v>
+        <v>122699987</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525314</v>
+        <v>524637</v>
       </c>
       <c r="R44" t="n">
-        <v>7020173</v>
+        <v>7020366</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122699987</v>
+        <v>122700027</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524637</v>
+        <v>525364</v>
       </c>
       <c r="R45" t="n">
-        <v>7020366</v>
+        <v>7020041</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,11 +5295,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5326,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700027</v>
+        <v>122700018</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,21 +5337,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5366,10 +5361,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525364</v>
+        <v>525314</v>
       </c>
       <c r="R46" t="n">
-        <v>7020041</v>
+        <v>7020173</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,6 +5397,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700009</v>
+        <v>122700031</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525066</v>
+        <v>524640</v>
       </c>
       <c r="R2" t="n">
-        <v>7020292</v>
+        <v>7020358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122699998</v>
+        <v>122700028</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524855</v>
+        <v>525342</v>
       </c>
       <c r="R3" t="n">
-        <v>7020387</v>
+        <v>7020049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700034</v>
+        <v>122700004</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525015</v>
+        <v>525112</v>
       </c>
       <c r="R4" t="n">
-        <v>7019776</v>
+        <v>7020339</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700002</v>
+        <v>122699994</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525076</v>
+        <v>524740</v>
       </c>
       <c r="R5" t="n">
-        <v>7020349</v>
+        <v>7020346</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700039</v>
+        <v>122699999</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525354</v>
+        <v>524951</v>
       </c>
       <c r="R6" t="n">
-        <v>7019963</v>
+        <v>7020351</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700017</v>
+        <v>122699992</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524976</v>
+        <v>524791</v>
       </c>
       <c r="R7" t="n">
-        <v>7020218</v>
+        <v>7020365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122699993</v>
+        <v>122700037</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524750</v>
+        <v>524743</v>
       </c>
       <c r="R8" t="n">
-        <v>7020358</v>
+        <v>7020378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700004</v>
+        <v>122700021</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525112</v>
+        <v>525319</v>
       </c>
       <c r="R9" t="n">
-        <v>7020339</v>
+        <v>7020073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700016</v>
+        <v>122700019</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524970</v>
+        <v>525451</v>
       </c>
       <c r="R10" t="n">
-        <v>7020222</v>
+        <v>7020169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122699997</v>
+        <v>122700020</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524808</v>
+        <v>525498</v>
       </c>
       <c r="R12" t="n">
-        <v>7020420</v>
+        <v>7020014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122699995</v>
+        <v>122700030</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524719</v>
+        <v>524857</v>
       </c>
       <c r="R13" t="n">
-        <v>7020350</v>
+        <v>7020120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700020</v>
+        <v>122700035</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525498</v>
+        <v>525057</v>
       </c>
       <c r="R15" t="n">
-        <v>7020014</v>
+        <v>7020101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700010</v>
+        <v>122699990</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2203,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525061</v>
+        <v>524886</v>
       </c>
       <c r="R16" t="n">
-        <v>7020296</v>
+        <v>7020196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122699994</v>
+        <v>122699987</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2310,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524740</v>
+        <v>524637</v>
       </c>
       <c r="R17" t="n">
-        <v>7020346</v>
+        <v>7020366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700035</v>
+        <v>122700005</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525057</v>
+        <v>525103</v>
       </c>
       <c r="R18" t="n">
-        <v>7020101</v>
+        <v>7020335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2438,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122699990</v>
+        <v>122699986</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2620,16 +2610,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524886</v>
+        <v>525217</v>
       </c>
       <c r="R20" t="n">
-        <v>7020196</v>
+        <v>7020178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2664,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122699996</v>
+        <v>122700039</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524805</v>
+        <v>525354</v>
       </c>
       <c r="R21" t="n">
-        <v>7020421</v>
+        <v>7019963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,11 +2767,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700031</v>
+        <v>122700008</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2833,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524640</v>
+        <v>525081</v>
       </c>
       <c r="R22" t="n">
-        <v>7020358</v>
+        <v>7020283</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,6 +2869,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2900,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700012</v>
+        <v>122700017</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2942,10 +2940,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524986</v>
+        <v>524976</v>
       </c>
       <c r="R23" t="n">
-        <v>7020251</v>
+        <v>7020218</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700006</v>
+        <v>122700027</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525089</v>
+        <v>525364</v>
       </c>
       <c r="R24" t="n">
-        <v>7020329</v>
+        <v>7020041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3083,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122699989</v>
+        <v>122700036</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3125,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524846</v>
+        <v>524700</v>
       </c>
       <c r="R25" t="n">
-        <v>7020185</v>
+        <v>7020267</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3185,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700024</v>
+        <v>122699988</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,16 +3227,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3263,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524639</v>
+        <v>524640</v>
       </c>
       <c r="R26" t="n">
-        <v>7020328</v>
+        <v>7020358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3291,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700022</v>
+        <v>122699989</v>
       </c>
       <c r="B27" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3330,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525086</v>
+        <v>524846</v>
       </c>
       <c r="R27" t="n">
-        <v>7019775</v>
+        <v>7020185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3394,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700037</v>
+        <v>122700029</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3472,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524743</v>
+        <v>525339</v>
       </c>
       <c r="R28" t="n">
-        <v>7020378</v>
+        <v>7020046</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3527,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700019</v>
+        <v>122700002</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3574,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525451</v>
+        <v>525076</v>
       </c>
       <c r="R29" t="n">
-        <v>7020169</v>
+        <v>7020349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3634,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700013</v>
+        <v>122700010</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3681,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524981</v>
+        <v>525061</v>
       </c>
       <c r="R30" t="n">
-        <v>7020231</v>
+        <v>7020296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700014</v>
+        <v>122700001</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3788,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524981</v>
+        <v>525052</v>
       </c>
       <c r="R31" t="n">
-        <v>7020235</v>
+        <v>7020331</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3821,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700033</v>
+        <v>122699993</v>
       </c>
       <c r="B32" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525450</v>
+        <v>524750</v>
       </c>
       <c r="R32" t="n">
-        <v>7019935</v>
+        <v>7020358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,6 +3924,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700001</v>
+        <v>122699997</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3997,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525052</v>
+        <v>524808</v>
       </c>
       <c r="R33" t="n">
-        <v>7020331</v>
+        <v>7020420</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699986</v>
+        <v>122700009</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4098,24 +4096,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525217</v>
+        <v>525066</v>
       </c>
       <c r="R34" t="n">
-        <v>7020178</v>
+        <v>7020292</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,7 +4142,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4179,7 +4169,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699992</v>
+        <v>122699991</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4219,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524791</v>
+        <v>524850</v>
       </c>
       <c r="R35" t="n">
-        <v>7020365</v>
+        <v>7020302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4259,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4286,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700029</v>
+        <v>122700025</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4326,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525339</v>
+        <v>525407</v>
       </c>
       <c r="R36" t="n">
-        <v>7020046</v>
+        <v>7020146</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,10 +4378,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700025</v>
+        <v>122699998</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,21 +4394,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4428,10 +4418,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525407</v>
+        <v>524855</v>
       </c>
       <c r="R37" t="n">
-        <v>7020146</v>
+        <v>7020387</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4464,6 +4454,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700008</v>
+        <v>122700026</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525081</v>
+        <v>525299</v>
       </c>
       <c r="R38" t="n">
-        <v>7020283</v>
+        <v>7019885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4561,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,10 +4587,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700032</v>
+        <v>122700024</v>
       </c>
       <c r="B39" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,21 +4603,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4627,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525024</v>
+        <v>524639</v>
       </c>
       <c r="R39" t="n">
-        <v>7020263</v>
+        <v>7020328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,6 +4663,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4694,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700036</v>
+        <v>122700032</v>
       </c>
       <c r="B40" t="n">
         <v>90962</v>
@@ -4739,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524700</v>
+        <v>525024</v>
       </c>
       <c r="R40" t="n">
-        <v>7020267</v>
+        <v>7020263</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700026</v>
+        <v>122700018</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4812,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4836,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525299</v>
+        <v>525314</v>
       </c>
       <c r="R41" t="n">
-        <v>7019885</v>
+        <v>7020173</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4877,6 +4872,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4903,7 +4903,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122699988</v>
+        <v>122700013</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524640</v>
+        <v>524981</v>
       </c>
       <c r="R42" t="n">
-        <v>7020358</v>
+        <v>7020231</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700030</v>
+        <v>122700007</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524857</v>
+        <v>525106</v>
       </c>
       <c r="R43" t="n">
-        <v>7020120</v>
+        <v>7020311</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,6 +5086,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5112,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122699987</v>
+        <v>122700016</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524637</v>
+        <v>524970</v>
       </c>
       <c r="R44" t="n">
-        <v>7020366</v>
+        <v>7020222</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,7 +5197,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700027</v>
+        <v>122700015</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5235,21 +5240,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5259,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525364</v>
+        <v>524981</v>
       </c>
       <c r="R45" t="n">
-        <v>7020041</v>
+        <v>7020235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,6 +5300,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5321,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700018</v>
+        <v>122699996</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5361,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525314</v>
+        <v>524805</v>
       </c>
       <c r="R46" t="n">
-        <v>7020173</v>
+        <v>7020421</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122699999</v>
+        <v>122700022</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5450,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5468,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524951</v>
+        <v>525086</v>
       </c>
       <c r="R47" t="n">
-        <v>7020351</v>
+        <v>7019775</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5504,11 +5514,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5535,10 +5540,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700028</v>
+        <v>122700034</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5551,21 +5556,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5575,10 +5580,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525342</v>
+        <v>525015</v>
       </c>
       <c r="R48" t="n">
-        <v>7020049</v>
+        <v>7019776</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700005</v>
+        <v>122700033</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5653,21 +5658,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525103</v>
+        <v>525450</v>
       </c>
       <c r="R49" t="n">
-        <v>7020335</v>
+        <v>7019935</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5713,11 +5718,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,7 +5744,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122699991</v>
+        <v>122699995</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524850</v>
+        <v>524719</v>
       </c>
       <c r="R50" t="n">
-        <v>7020302</v>
+        <v>7020350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5851,7 +5851,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700007</v>
+        <v>122700006</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525106</v>
+        <v>525089</v>
       </c>
       <c r="R51" t="n">
-        <v>7020311</v>
+        <v>7020329</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700021</v>
+        <v>122700012</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525319</v>
+        <v>524986</v>
       </c>
       <c r="R52" t="n">
-        <v>7020073</v>
+        <v>7020251</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700031</v>
+        <v>122700028</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524640</v>
+        <v>525342</v>
       </c>
       <c r="R2" t="n">
-        <v>7020358</v>
+        <v>7020049</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700028</v>
+        <v>122700031</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525342</v>
+        <v>524640</v>
       </c>
       <c r="R3" t="n">
-        <v>7020049</v>
+        <v>7020358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700005</v>
+        <v>122699986</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2396,16 +2396,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525103</v>
+        <v>525217</v>
       </c>
       <c r="R18" t="n">
-        <v>7020335</v>
+        <v>7020178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2450,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700003</v>
+        <v>122700005</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2509,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525101</v>
+        <v>525103</v>
       </c>
       <c r="R19" t="n">
-        <v>7020350</v>
+        <v>7020335</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,7 +2584,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122699986</v>
+        <v>122700003</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2610,24 +2618,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525217</v>
+        <v>525101</v>
       </c>
       <c r="R20" t="n">
-        <v>7020178</v>
+        <v>7020350</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700027</v>
+        <v>122700036</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525364</v>
+        <v>524700</v>
       </c>
       <c r="R24" t="n">
-        <v>7020041</v>
+        <v>7020267</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700036</v>
+        <v>122700027</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524700</v>
+        <v>525364</v>
       </c>
       <c r="R25" t="n">
-        <v>7020267</v>
+        <v>7020041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700002</v>
+        <v>122700010</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525076</v>
+        <v>525061</v>
       </c>
       <c r="R29" t="n">
-        <v>7020349</v>
+        <v>7020296</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700010</v>
+        <v>122700001</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525061</v>
+        <v>525052</v>
       </c>
       <c r="R30" t="n">
-        <v>7020296</v>
+        <v>7020331</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700001</v>
+        <v>122699993</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525052</v>
+        <v>524750</v>
       </c>
       <c r="R31" t="n">
-        <v>7020331</v>
+        <v>7020358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122699993</v>
+        <v>122699997</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524750</v>
+        <v>524808</v>
       </c>
       <c r="R32" t="n">
-        <v>7020358</v>
+        <v>7020420</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122699997</v>
+        <v>122700002</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524808</v>
+        <v>525076</v>
       </c>
       <c r="R33" t="n">
-        <v>7020420</v>
+        <v>7020349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -3527,7 +3527,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700010</v>
+        <v>122699993</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525061</v>
+        <v>524750</v>
       </c>
       <c r="R29" t="n">
-        <v>7020296</v>
+        <v>7020358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700001</v>
+        <v>122699997</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525052</v>
+        <v>524808</v>
       </c>
       <c r="R30" t="n">
-        <v>7020331</v>
+        <v>7020420</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122699993</v>
+        <v>122700010</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524750</v>
+        <v>525061</v>
       </c>
       <c r="R31" t="n">
-        <v>7020358</v>
+        <v>7020296</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122699997</v>
+        <v>122700002</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524808</v>
+        <v>525076</v>
       </c>
       <c r="R32" t="n">
-        <v>7020420</v>
+        <v>7020349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700002</v>
+        <v>122700001</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525076</v>
+        <v>525052</v>
       </c>
       <c r="R33" t="n">
-        <v>7020349</v>
+        <v>7020331</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700022</v>
+        <v>122700034</v>
       </c>
       <c r="B47" t="n">
-        <v>90955</v>
+        <v>90962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5450,25 +5450,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525086</v>
+        <v>525015</v>
       </c>
       <c r="R47" t="n">
-        <v>7019775</v>
+        <v>7019776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700034</v>
+        <v>122700033</v>
       </c>
       <c r="B48" t="n">
         <v>90962</v>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525015</v>
+        <v>525450</v>
       </c>
       <c r="R48" t="n">
-        <v>7019776</v>
+        <v>7019935</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700033</v>
+        <v>122700022</v>
       </c>
       <c r="B49" t="n">
-        <v>90962</v>
+        <v>90955</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5654,25 +5654,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525450</v>
+        <v>525086</v>
       </c>
       <c r="R49" t="n">
-        <v>7019935</v>
+        <v>7019775</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700028</v>
+        <v>122699999</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525342</v>
+        <v>524951</v>
       </c>
       <c r="R2" t="n">
-        <v>7020049</v>
+        <v>7020351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700031</v>
+        <v>122700008</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524640</v>
+        <v>525081</v>
       </c>
       <c r="R3" t="n">
-        <v>7020358</v>
+        <v>7020283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700004</v>
+        <v>122700007</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525112</v>
+        <v>525106</v>
       </c>
       <c r="R4" t="n">
-        <v>7020339</v>
+        <v>7020311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122699994</v>
+        <v>122700035</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524740</v>
+        <v>525057</v>
       </c>
       <c r="R5" t="n">
-        <v>7020346</v>
+        <v>7020101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122699999</v>
+        <v>122700034</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524951</v>
+        <v>525015</v>
       </c>
       <c r="R6" t="n">
-        <v>7020351</v>
+        <v>7019776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122699992</v>
+        <v>122700029</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524791</v>
+        <v>525339</v>
       </c>
       <c r="R7" t="n">
-        <v>7020365</v>
+        <v>7020046</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700037</v>
+        <v>122700004</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524743</v>
+        <v>525112</v>
       </c>
       <c r="R8" t="n">
-        <v>7020378</v>
+        <v>7020339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700021</v>
+        <v>122699992</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525319</v>
+        <v>524791</v>
       </c>
       <c r="R9" t="n">
-        <v>7020073</v>
+        <v>7020365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700019</v>
+        <v>122700001</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525451</v>
+        <v>525052</v>
       </c>
       <c r="R10" t="n">
-        <v>7020169</v>
+        <v>7020331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700000</v>
+        <v>122700005</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524963</v>
+        <v>525103</v>
       </c>
       <c r="R11" t="n">
-        <v>7020373</v>
+        <v>7020335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700020</v>
+        <v>122700017</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525498</v>
+        <v>524976</v>
       </c>
       <c r="R12" t="n">
-        <v>7020014</v>
+        <v>7020218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700030</v>
+        <v>122699988</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524857</v>
+        <v>524640</v>
       </c>
       <c r="R13" t="n">
-        <v>7020120</v>
+        <v>7020358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700023</v>
+        <v>122699998</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,16 +1960,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525274</v>
+        <v>524855</v>
       </c>
       <c r="R14" t="n">
-        <v>7020074</v>
+        <v>7020387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700035</v>
+        <v>122700010</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525057</v>
+        <v>525061</v>
       </c>
       <c r="R15" t="n">
-        <v>7020101</v>
+        <v>7020296</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2127,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122699990</v>
+        <v>122700000</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2188,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524886</v>
+        <v>524963</v>
       </c>
       <c r="R16" t="n">
-        <v>7020196</v>
+        <v>7020373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122699987</v>
+        <v>122700030</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524637</v>
+        <v>524857</v>
       </c>
       <c r="R17" t="n">
-        <v>7020366</v>
+        <v>7020120</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122699986</v>
+        <v>122700019</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2396,24 +2401,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525217</v>
+        <v>525451</v>
       </c>
       <c r="R18" t="n">
-        <v>7020178</v>
+        <v>7020169</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700005</v>
+        <v>122700002</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2517,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525103</v>
+        <v>525076</v>
       </c>
       <c r="R19" t="n">
-        <v>7020335</v>
+        <v>7020349</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700003</v>
+        <v>122700024</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,16 +2597,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2624,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525101</v>
+        <v>524639</v>
       </c>
       <c r="R20" t="n">
-        <v>7020350</v>
+        <v>7020328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700039</v>
+        <v>122700020</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525354</v>
+        <v>525498</v>
       </c>
       <c r="R21" t="n">
-        <v>7019963</v>
+        <v>7020014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,6 +2764,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700008</v>
+        <v>122700037</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2833,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525081</v>
+        <v>524743</v>
       </c>
       <c r="R22" t="n">
-        <v>7020283</v>
+        <v>7020378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,11 +2871,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700017</v>
+        <v>122700021</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2940,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524976</v>
+        <v>525319</v>
       </c>
       <c r="R23" t="n">
-        <v>7020218</v>
+        <v>7020073</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2977,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3010,7 +3007,7 @@
         <v>122700036</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,7 +3208,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122699988</v>
+        <v>122700006</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3251,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524640</v>
+        <v>525089</v>
       </c>
       <c r="R26" t="n">
-        <v>7020358</v>
+        <v>7020329</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122699989</v>
+        <v>122700039</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,21 +3331,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3358,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524846</v>
+        <v>525354</v>
       </c>
       <c r="R27" t="n">
-        <v>7020185</v>
+        <v>7019963</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,11 +3391,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700029</v>
+        <v>122700018</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3433,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3465,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525339</v>
+        <v>525314</v>
       </c>
       <c r="R28" t="n">
-        <v>7020046</v>
+        <v>7020173</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,6 +3493,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3527,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122699993</v>
+        <v>122700022</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3539,25 +3536,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3567,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524750</v>
+        <v>525086</v>
       </c>
       <c r="R29" t="n">
-        <v>7020358</v>
+        <v>7019775</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3603,11 +3600,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3634,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122699997</v>
+        <v>122700026</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,21 +3642,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524808</v>
+        <v>525299</v>
       </c>
       <c r="R30" t="n">
-        <v>7020420</v>
+        <v>7019885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,11 +3702,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3741,7 +3728,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700010</v>
+        <v>122699991</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3781,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525061</v>
+        <v>524850</v>
       </c>
       <c r="R31" t="n">
-        <v>7020296</v>
+        <v>7020302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,7 +3808,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700002</v>
+        <v>122700028</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,21 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525076</v>
+        <v>525342</v>
       </c>
       <c r="R32" t="n">
-        <v>7020349</v>
+        <v>7020049</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,11 +3911,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,7 +3937,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700001</v>
+        <v>122699986</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3989,16 +3971,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525052</v>
+        <v>525217</v>
       </c>
       <c r="R33" t="n">
-        <v>7020331</v>
+        <v>7020178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,7 +4025,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4052,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700009</v>
+        <v>122699997</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4102,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525066</v>
+        <v>524808</v>
       </c>
       <c r="R34" t="n">
-        <v>7020292</v>
+        <v>7020420</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4159,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699991</v>
+        <v>122699987</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4209,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524850</v>
+        <v>524637</v>
       </c>
       <c r="R35" t="n">
-        <v>7020302</v>
+        <v>7020366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4239,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,10 +4266,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700025</v>
+        <v>122699989</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4292,21 +4282,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4316,10 +4306,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525407</v>
+        <v>524846</v>
       </c>
       <c r="R36" t="n">
-        <v>7020146</v>
+        <v>7020185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4352,6 +4342,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,7 +4373,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122699998</v>
+        <v>122700014</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4418,10 +4413,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524855</v>
+        <v>524981</v>
       </c>
       <c r="R37" t="n">
-        <v>7020387</v>
+        <v>7020235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4453,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,10 +4480,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700026</v>
+        <v>122700003</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,21 +4496,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4525,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525299</v>
+        <v>525101</v>
       </c>
       <c r="R38" t="n">
-        <v>7019885</v>
+        <v>7020350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4561,6 +4556,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4587,10 +4587,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700024</v>
+        <v>122699990</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4603,16 +4603,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524639</v>
+        <v>524886</v>
       </c>
       <c r="R39" t="n">
-        <v>7020328</v>
+        <v>7020196</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4694,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700032</v>
+        <v>122699994</v>
       </c>
       <c r="B40" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4710,21 +4710,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525024</v>
+        <v>524740</v>
       </c>
       <c r="R40" t="n">
-        <v>7020263</v>
+        <v>7020346</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,6 +4770,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4796,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700018</v>
+        <v>122700032</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4812,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4836,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525314</v>
+        <v>525024</v>
       </c>
       <c r="R41" t="n">
-        <v>7020173</v>
+        <v>7020263</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,11 +4877,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4903,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700013</v>
+        <v>122700023</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4919,16 +4919,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524981</v>
+        <v>525274</v>
       </c>
       <c r="R42" t="n">
-        <v>7020231</v>
+        <v>7020074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5010,7 +5010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700007</v>
+        <v>122700009</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525106</v>
+        <v>525066</v>
       </c>
       <c r="R43" t="n">
-        <v>7020311</v>
+        <v>7020292</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700016</v>
+        <v>122700013</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524970</v>
+        <v>524981</v>
       </c>
       <c r="R44" t="n">
-        <v>7020222</v>
+        <v>7020231</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700015</v>
+        <v>122699996</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524981</v>
+        <v>524805</v>
       </c>
       <c r="R45" t="n">
-        <v>7020235</v>
+        <v>7020421</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122699996</v>
+        <v>122700031</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524805</v>
+        <v>524640</v>
       </c>
       <c r="R46" t="n">
-        <v>7020421</v>
+        <v>7020358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,11 +5407,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700034</v>
+        <v>122700025</v>
       </c>
       <c r="B47" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,21 +5449,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525015</v>
+        <v>525407</v>
       </c>
       <c r="R47" t="n">
-        <v>7019776</v>
+        <v>7020146</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5540,10 +5535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700033</v>
+        <v>122700012</v>
       </c>
       <c r="B48" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5556,21 +5551,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525450</v>
+        <v>524986</v>
       </c>
       <c r="R48" t="n">
-        <v>7019935</v>
+        <v>7020251</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,6 +5611,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700022</v>
+        <v>122700016</v>
       </c>
       <c r="B49" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5654,25 +5654,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525086</v>
+        <v>524970</v>
       </c>
       <c r="R49" t="n">
-        <v>7019775</v>
+        <v>7020222</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5718,6 +5718,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,10 +5749,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122699995</v>
+        <v>122700033</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5760,21 +5765,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524719</v>
+        <v>525450</v>
       </c>
       <c r="R50" t="n">
-        <v>7020350</v>
+        <v>7019935</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5820,11 +5825,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5851,7 +5851,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700006</v>
+        <v>122699993</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525089</v>
+        <v>524750</v>
       </c>
       <c r="R51" t="n">
-        <v>7020329</v>
+        <v>7020358</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700012</v>
+        <v>122699995</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524986</v>
+        <v>524719</v>
       </c>
       <c r="R52" t="n">
-        <v>7020251</v>
+        <v>7020350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122699999</v>
+        <v>122700008</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524951</v>
+        <v>525081</v>
       </c>
       <c r="R2" t="n">
-        <v>7020351</v>
+        <v>7020283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700008</v>
+        <v>122699999</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525081</v>
+        <v>524951</v>
       </c>
       <c r="R3" t="n">
-        <v>7020283</v>
+        <v>7020351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700034</v>
+        <v>122699992</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525015</v>
+        <v>524791</v>
       </c>
       <c r="R6" t="n">
-        <v>7019776</v>
+        <v>7020365</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700029</v>
+        <v>122700034</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525339</v>
+        <v>525015</v>
       </c>
       <c r="R7" t="n">
-        <v>7020046</v>
+        <v>7019776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700004</v>
+        <v>122700029</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525112</v>
+        <v>525339</v>
       </c>
       <c r="R8" t="n">
-        <v>7020339</v>
+        <v>7020046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122699992</v>
+        <v>122700004</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524791</v>
+        <v>525112</v>
       </c>
       <c r="R9" t="n">
-        <v>7020365</v>
+        <v>7020339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700005</v>
+        <v>122699988</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525103</v>
+        <v>524640</v>
       </c>
       <c r="R11" t="n">
-        <v>7020335</v>
+        <v>7020358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700017</v>
+        <v>122699998</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524976</v>
+        <v>524855</v>
       </c>
       <c r="R12" t="n">
-        <v>7020218</v>
+        <v>7020387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122699988</v>
+        <v>122700005</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524640</v>
+        <v>525103</v>
       </c>
       <c r="R13" t="n">
-        <v>7020358</v>
+        <v>7020335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122699998</v>
+        <v>122700010</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524855</v>
+        <v>525061</v>
       </c>
       <c r="R14" t="n">
-        <v>7020387</v>
+        <v>7020296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700010</v>
+        <v>122700017</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525061</v>
+        <v>524976</v>
       </c>
       <c r="R15" t="n">
-        <v>7020296</v>
+        <v>7020218</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700000</v>
+        <v>122700030</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524963</v>
+        <v>524857</v>
       </c>
       <c r="R16" t="n">
-        <v>7020373</v>
+        <v>7020120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700030</v>
+        <v>122700000</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524857</v>
+        <v>524963</v>
       </c>
       <c r="R17" t="n">
-        <v>7020120</v>
+        <v>7020373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700021</v>
+        <v>122700036</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525319</v>
+        <v>524700</v>
       </c>
       <c r="R23" t="n">
-        <v>7020073</v>
+        <v>7020267</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,11 +2973,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700036</v>
+        <v>122700027</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524700</v>
+        <v>525364</v>
       </c>
       <c r="R24" t="n">
-        <v>7020267</v>
+        <v>7020041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700027</v>
+        <v>122700021</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525364</v>
+        <v>525319</v>
       </c>
       <c r="R25" t="n">
-        <v>7020041</v>
+        <v>7020073</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,6 +3177,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700013</v>
+        <v>122699996</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524981</v>
+        <v>524805</v>
       </c>
       <c r="R44" t="n">
-        <v>7020231</v>
+        <v>7020421</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122699996</v>
+        <v>122700013</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524805</v>
+        <v>524981</v>
       </c>
       <c r="R45" t="n">
-        <v>7020421</v>
+        <v>7020231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700025</v>
+        <v>122700016</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5449,21 +5449,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525407</v>
+        <v>524970</v>
       </c>
       <c r="R47" t="n">
-        <v>7020146</v>
+        <v>7020222</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5509,6 +5509,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5535,10 +5540,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700012</v>
+        <v>122700025</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5551,21 +5556,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5575,10 +5580,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524986</v>
+        <v>525407</v>
       </c>
       <c r="R48" t="n">
-        <v>7020251</v>
+        <v>7020146</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,11 +5616,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700016</v>
+        <v>122700012</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524970</v>
+        <v>524986</v>
       </c>
       <c r="R49" t="n">
-        <v>7020222</v>
+        <v>7020251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700008</v>
+        <v>122700034</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525081</v>
+        <v>525015</v>
       </c>
       <c r="R2" t="n">
-        <v>7020283</v>
+        <v>7019776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122699999</v>
+        <v>122700035</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524951</v>
+        <v>525057</v>
       </c>
       <c r="R3" t="n">
-        <v>7020351</v>
+        <v>7020101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700007</v>
+        <v>122700036</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525106</v>
+        <v>524700</v>
       </c>
       <c r="R4" t="n">
-        <v>7020311</v>
+        <v>7020267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700035</v>
+        <v>122700018</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525057</v>
+        <v>525314</v>
       </c>
       <c r="R5" t="n">
-        <v>7020101</v>
+        <v>7020173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700034</v>
+        <v>122700016</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525015</v>
+        <v>524970</v>
       </c>
       <c r="R7" t="n">
-        <v>7019776</v>
+        <v>7020222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700029</v>
+        <v>122700004</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525339</v>
+        <v>525112</v>
       </c>
       <c r="R8" t="n">
-        <v>7020046</v>
+        <v>7020339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122700004</v>
+        <v>122699998</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525112</v>
+        <v>524855</v>
       </c>
       <c r="R9" t="n">
-        <v>7020339</v>
+        <v>7020387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700001</v>
+        <v>122699994</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525052</v>
+        <v>524740</v>
       </c>
       <c r="R10" t="n">
-        <v>7020331</v>
+        <v>7020346</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122699988</v>
+        <v>122700037</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524640</v>
+        <v>524743</v>
       </c>
       <c r="R11" t="n">
-        <v>7020358</v>
+        <v>7020378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122699998</v>
+        <v>122700003</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524855</v>
+        <v>525101</v>
       </c>
       <c r="R12" t="n">
-        <v>7020387</v>
+        <v>7020350</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700005</v>
+        <v>122700001</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525103</v>
+        <v>525052</v>
       </c>
       <c r="R13" t="n">
-        <v>7020335</v>
+        <v>7020331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700010</v>
+        <v>122700024</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,16 +1955,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525061</v>
+        <v>524639</v>
       </c>
       <c r="R14" t="n">
-        <v>7020296</v>
+        <v>7020328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700017</v>
+        <v>122699995</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524976</v>
+        <v>524719</v>
       </c>
       <c r="R15" t="n">
-        <v>7020218</v>
+        <v>7020350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700030</v>
+        <v>122700022</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524857</v>
+        <v>525086</v>
       </c>
       <c r="R16" t="n">
-        <v>7020120</v>
+        <v>7019775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700000</v>
+        <v>122700026</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524963</v>
+        <v>525299</v>
       </c>
       <c r="R17" t="n">
-        <v>7020373</v>
+        <v>7019885</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700019</v>
+        <v>122700005</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525451</v>
+        <v>525103</v>
       </c>
       <c r="R18" t="n">
-        <v>7020169</v>
+        <v>7020335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700002</v>
+        <v>122700025</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525076</v>
+        <v>525407</v>
       </c>
       <c r="R19" t="n">
-        <v>7020349</v>
+        <v>7020146</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700024</v>
+        <v>122700014</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,16 +2582,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2621,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524639</v>
+        <v>524981</v>
       </c>
       <c r="R20" t="n">
-        <v>7020328</v>
+        <v>7020235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2646,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700020</v>
+        <v>122699990</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2728,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525498</v>
+        <v>524886</v>
       </c>
       <c r="R21" t="n">
-        <v>7020014</v>
+        <v>7020196</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700037</v>
+        <v>122700033</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524743</v>
+        <v>525450</v>
       </c>
       <c r="R22" t="n">
-        <v>7020378</v>
+        <v>7019935</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700036</v>
+        <v>122700019</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524700</v>
+        <v>525451</v>
       </c>
       <c r="R23" t="n">
-        <v>7020267</v>
+        <v>7020169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2958,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700027</v>
+        <v>122700012</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525364</v>
+        <v>524986</v>
       </c>
       <c r="R24" t="n">
-        <v>7020041</v>
+        <v>7020251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3065,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3101,7 +3096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700021</v>
+        <v>122699991</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3141,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525319</v>
+        <v>524850</v>
       </c>
       <c r="R25" t="n">
-        <v>7020073</v>
+        <v>7020302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700006</v>
+        <v>122699988</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525089</v>
+        <v>524640</v>
       </c>
       <c r="R26" t="n">
-        <v>7020329</v>
+        <v>7020358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700039</v>
+        <v>122700032</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525354</v>
+        <v>525024</v>
       </c>
       <c r="R27" t="n">
-        <v>7019963</v>
+        <v>7020263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700018</v>
+        <v>122700031</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525314</v>
+        <v>524640</v>
       </c>
       <c r="R28" t="n">
-        <v>7020173</v>
+        <v>7020358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,11 +3488,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700022</v>
+        <v>122700039</v>
       </c>
       <c r="B29" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3536,25 +3526,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3564,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525086</v>
+        <v>525354</v>
       </c>
       <c r="R29" t="n">
-        <v>7019775</v>
+        <v>7019963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700026</v>
+        <v>122700008</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3666,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525299</v>
+        <v>525081</v>
       </c>
       <c r="R30" t="n">
-        <v>7019885</v>
+        <v>7020283</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3702,6 +3692,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122699991</v>
+        <v>122700023</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3744,16 +3739,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524850</v>
+        <v>525274</v>
       </c>
       <c r="R31" t="n">
-        <v>7020302</v>
+        <v>7020074</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700028</v>
+        <v>122700020</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,21 +3846,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525342</v>
+        <v>525498</v>
       </c>
       <c r="R32" t="n">
-        <v>7020049</v>
+        <v>7020014</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,6 +3906,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,7 +3937,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122699986</v>
+        <v>122700002</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3971,24 +3971,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525217</v>
+        <v>525076</v>
       </c>
       <c r="R33" t="n">
-        <v>7020178</v>
+        <v>7020349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,7 +4017,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,7 +4044,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699997</v>
+        <v>122699993</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4092,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524808</v>
+        <v>524750</v>
       </c>
       <c r="R34" t="n">
-        <v>7020420</v>
+        <v>7020358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,7 +4365,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700014</v>
+        <v>122699986</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4407,16 +4399,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524981</v>
+        <v>525217</v>
       </c>
       <c r="R37" t="n">
-        <v>7020235</v>
+        <v>7020178</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4480,7 +4480,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700003</v>
+        <v>122699997</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525101</v>
+        <v>524808</v>
       </c>
       <c r="R38" t="n">
-        <v>7020350</v>
+        <v>7020420</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4587,7 +4587,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122699990</v>
+        <v>122699999</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524886</v>
+        <v>524951</v>
       </c>
       <c r="R39" t="n">
-        <v>7020196</v>
+        <v>7020351</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122699994</v>
+        <v>122700009</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524740</v>
+        <v>525066</v>
       </c>
       <c r="R40" t="n">
-        <v>7020346</v>
+        <v>7020292</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700032</v>
+        <v>122700007</v>
       </c>
       <c r="B41" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525024</v>
+        <v>525106</v>
       </c>
       <c r="R41" t="n">
-        <v>7020263</v>
+        <v>7020311</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4877,6 +4877,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4903,10 +4908,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700023</v>
+        <v>122700030</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4919,21 +4924,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525274</v>
+        <v>524857</v>
       </c>
       <c r="R42" t="n">
-        <v>7020074</v>
+        <v>7020120</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,11 +4984,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5010,7 +5010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700009</v>
+        <v>122699996</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525066</v>
+        <v>524805</v>
       </c>
       <c r="R43" t="n">
-        <v>7020292</v>
+        <v>7020421</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122699996</v>
+        <v>122700010</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524805</v>
+        <v>525061</v>
       </c>
       <c r="R44" t="n">
-        <v>7020421</v>
+        <v>7020296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700013</v>
+        <v>122700000</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524981</v>
+        <v>524963</v>
       </c>
       <c r="R45" t="n">
-        <v>7020231</v>
+        <v>7020373</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700031</v>
+        <v>122700028</v>
       </c>
       <c r="B46" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524640</v>
+        <v>525342</v>
       </c>
       <c r="R46" t="n">
-        <v>7020358</v>
+        <v>7020049</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5433,7 +5433,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700016</v>
+        <v>122700006</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524970</v>
+        <v>525089</v>
       </c>
       <c r="R47" t="n">
-        <v>7020222</v>
+        <v>7020329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700025</v>
+        <v>122700017</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525407</v>
+        <v>524976</v>
       </c>
       <c r="R48" t="n">
-        <v>7020146</v>
+        <v>7020218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,6 +5616,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5642,7 +5647,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700012</v>
+        <v>122700013</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524986</v>
+        <v>524981</v>
       </c>
       <c r="R49" t="n">
-        <v>7020251</v>
+        <v>7020231</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5749,10 +5754,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700033</v>
+        <v>122700029</v>
       </c>
       <c r="B50" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5765,21 +5770,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5789,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525450</v>
+        <v>525339</v>
       </c>
       <c r="R50" t="n">
-        <v>7019935</v>
+        <v>7020046</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5851,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122699993</v>
+        <v>122700027</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,21 +5872,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5891,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524750</v>
+        <v>525364</v>
       </c>
       <c r="R51" t="n">
-        <v>7020358</v>
+        <v>7020041</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5927,11 +5932,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122699995</v>
+        <v>122700021</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524719</v>
+        <v>525319</v>
       </c>
       <c r="R52" t="n">
-        <v>7020350</v>
+        <v>7020073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700036</v>
+        <v>122700018</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524700</v>
+        <v>525314</v>
       </c>
       <c r="R4" t="n">
-        <v>7020267</v>
+        <v>7020173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700018</v>
+        <v>122700036</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525314</v>
+        <v>524700</v>
       </c>
       <c r="R5" t="n">
-        <v>7020173</v>
+        <v>7020267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700016</v>
+        <v>122700004</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524970</v>
+        <v>525112</v>
       </c>
       <c r="R7" t="n">
-        <v>7020222</v>
+        <v>7020339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700004</v>
+        <v>122700016</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525112</v>
+        <v>524970</v>
       </c>
       <c r="R8" t="n">
-        <v>7020339</v>
+        <v>7020222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700022</v>
+        <v>122700026</v>
       </c>
       <c r="B16" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525086</v>
+        <v>525299</v>
       </c>
       <c r="R16" t="n">
-        <v>7019775</v>
+        <v>7019885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700026</v>
+        <v>122700022</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525299</v>
+        <v>525086</v>
       </c>
       <c r="R17" t="n">
-        <v>7019885</v>
+        <v>7019775</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122699996</v>
+        <v>122700010</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524805</v>
+        <v>525061</v>
       </c>
       <c r="R43" t="n">
-        <v>7020421</v>
+        <v>7020296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700010</v>
+        <v>122699996</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525061</v>
+        <v>524805</v>
       </c>
       <c r="R44" t="n">
-        <v>7020296</v>
+        <v>7020421</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700000</v>
+        <v>122700028</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524963</v>
+        <v>525342</v>
       </c>
       <c r="R45" t="n">
-        <v>7020373</v>
+        <v>7020049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,11 +5300,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,10 +5326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700028</v>
+        <v>122700006</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5342,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525342</v>
+        <v>525089</v>
       </c>
       <c r="R46" t="n">
-        <v>7020049</v>
+        <v>7020329</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,6 +5402,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700006</v>
+        <v>122700000</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525089</v>
+        <v>524963</v>
       </c>
       <c r="R47" t="n">
-        <v>7020329</v>
+        <v>7020373</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700026</v>
+        <v>122700022</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525299</v>
+        <v>525086</v>
       </c>
       <c r="R16" t="n">
-        <v>7019885</v>
+        <v>7019775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700022</v>
+        <v>122700026</v>
       </c>
       <c r="B17" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525086</v>
+        <v>525299</v>
       </c>
       <c r="R17" t="n">
-        <v>7019775</v>
+        <v>7019885</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122700025</v>
+        <v>122699990</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525407</v>
+        <v>524886</v>
       </c>
       <c r="R19" t="n">
-        <v>7020146</v>
+        <v>7020196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700014</v>
+        <v>122700025</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524981</v>
+        <v>525407</v>
       </c>
       <c r="R20" t="n">
-        <v>7020235</v>
+        <v>7020146</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122699990</v>
+        <v>122700014</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524886</v>
+        <v>524981</v>
       </c>
       <c r="R21" t="n">
-        <v>7020196</v>
+        <v>7020235</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122700034</v>
+        <v>122699995</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525015</v>
+        <v>524719</v>
       </c>
       <c r="R2" t="n">
-        <v>7019776</v>
+        <v>7020350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700035</v>
+        <v>122699991</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525057</v>
+        <v>524850</v>
       </c>
       <c r="R3" t="n">
-        <v>7020101</v>
+        <v>7020302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700018</v>
+        <v>122700034</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525314</v>
+        <v>525015</v>
       </c>
       <c r="R4" t="n">
-        <v>7020173</v>
+        <v>7019776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700036</v>
+        <v>122700013</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524700</v>
+        <v>524981</v>
       </c>
       <c r="R5" t="n">
-        <v>7020267</v>
+        <v>7020231</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122699992</v>
+        <v>122700003</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524791</v>
+        <v>525101</v>
       </c>
       <c r="R6" t="n">
-        <v>7020365</v>
+        <v>7020350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700004</v>
+        <v>122699989</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525112</v>
+        <v>524846</v>
       </c>
       <c r="R7" t="n">
-        <v>7020339</v>
+        <v>7020185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700016</v>
+        <v>122700014</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524970</v>
+        <v>524981</v>
       </c>
       <c r="R8" t="n">
-        <v>7020222</v>
+        <v>7020235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122699998</v>
+        <v>122699999</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1449,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524855</v>
+        <v>524951</v>
       </c>
       <c r="R9" t="n">
-        <v>7020387</v>
+        <v>7020351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122699994</v>
+        <v>122700018</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1556,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524740</v>
+        <v>525314</v>
       </c>
       <c r="R10" t="n">
-        <v>7020346</v>
+        <v>7020173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700037</v>
+        <v>122700039</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1663,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524743</v>
+        <v>525354</v>
       </c>
       <c r="R11" t="n">
-        <v>7020378</v>
+        <v>7019963</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122700003</v>
+        <v>122699988</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1765,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525101</v>
+        <v>524640</v>
       </c>
       <c r="R12" t="n">
-        <v>7020350</v>
+        <v>7020358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700001</v>
+        <v>122700012</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525052</v>
+        <v>524986</v>
       </c>
       <c r="R13" t="n">
-        <v>7020331</v>
+        <v>7020251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700024</v>
+        <v>122700007</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524639</v>
+        <v>525106</v>
       </c>
       <c r="R14" t="n">
-        <v>7020328</v>
+        <v>7020311</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122699995</v>
+        <v>122700026</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524719</v>
+        <v>525299</v>
       </c>
       <c r="R15" t="n">
-        <v>7020350</v>
+        <v>7019885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122700022</v>
+        <v>122699987</v>
       </c>
       <c r="B16" t="n">
-        <v>90963</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525086</v>
+        <v>524637</v>
       </c>
       <c r="R16" t="n">
-        <v>7019775</v>
+        <v>7020366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122700026</v>
+        <v>122699994</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525299</v>
+        <v>524740</v>
       </c>
       <c r="R17" t="n">
-        <v>7019885</v>
+        <v>7020346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122700005</v>
+        <v>122699990</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2397,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525103</v>
+        <v>524886</v>
       </c>
       <c r="R18" t="n">
-        <v>7020335</v>
+        <v>7020196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122699990</v>
+        <v>122699997</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2504,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524886</v>
+        <v>524808</v>
       </c>
       <c r="R19" t="n">
-        <v>7020196</v>
+        <v>7020420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122700025</v>
+        <v>122699996</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525407</v>
+        <v>524805</v>
       </c>
       <c r="R20" t="n">
-        <v>7020146</v>
+        <v>7020421</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700014</v>
+        <v>122700008</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2713,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524981</v>
+        <v>525081</v>
       </c>
       <c r="R21" t="n">
-        <v>7020235</v>
+        <v>7020283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700033</v>
+        <v>122700021</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525450</v>
+        <v>525319</v>
       </c>
       <c r="R22" t="n">
-        <v>7019935</v>
+        <v>7020073</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122700019</v>
+        <v>122699998</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2922,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525451</v>
+        <v>524855</v>
       </c>
       <c r="R23" t="n">
-        <v>7020169</v>
+        <v>7020387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122700012</v>
+        <v>122699993</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3029,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524986</v>
+        <v>524750</v>
       </c>
       <c r="R24" t="n">
-        <v>7020251</v>
+        <v>7020358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122699991</v>
+        <v>122700032</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524850</v>
+        <v>525024</v>
       </c>
       <c r="R25" t="n">
-        <v>7020302</v>
+        <v>7020263</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,11 +3197,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122699988</v>
+        <v>122700031</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3279,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700032</v>
+        <v>122700035</v>
       </c>
       <c r="B27" t="n">
         <v>90970</v>
@@ -3350,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525024</v>
+        <v>525057</v>
       </c>
       <c r="R27" t="n">
-        <v>7020263</v>
+        <v>7020101</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700031</v>
+        <v>122700016</v>
       </c>
       <c r="B28" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3443,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524640</v>
+        <v>524970</v>
       </c>
       <c r="R28" t="n">
-        <v>7020358</v>
+        <v>7020222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,6 +3503,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122700039</v>
+        <v>122699992</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525354</v>
+        <v>524791</v>
       </c>
       <c r="R29" t="n">
-        <v>7019963</v>
+        <v>7020365</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700008</v>
+        <v>122700019</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3656,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525081</v>
+        <v>525451</v>
       </c>
       <c r="R30" t="n">
-        <v>7020283</v>
+        <v>7020169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700023</v>
+        <v>122700017</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,16 +3764,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3763,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525274</v>
+        <v>524976</v>
       </c>
       <c r="R31" t="n">
-        <v>7020074</v>
+        <v>7020218</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3803,7 +3828,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700020</v>
+        <v>122700000</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3870,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525498</v>
+        <v>524963</v>
       </c>
       <c r="R32" t="n">
-        <v>7020014</v>
+        <v>7020373</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3937,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700002</v>
+        <v>122700027</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3977,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525076</v>
+        <v>525364</v>
       </c>
       <c r="R33" t="n">
-        <v>7020349</v>
+        <v>7020041</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,11 +4038,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699993</v>
+        <v>122700022</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4076,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524750</v>
+        <v>525086</v>
       </c>
       <c r="R34" t="n">
-        <v>7020358</v>
+        <v>7019775</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,11 +4140,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,10 +4166,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699987</v>
+        <v>122700029</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,21 +4182,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524637</v>
+        <v>525339</v>
       </c>
       <c r="R35" t="n">
-        <v>7020366</v>
+        <v>7020046</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,11 +4242,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122699989</v>
+        <v>122700006</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4298,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524846</v>
+        <v>525089</v>
       </c>
       <c r="R36" t="n">
-        <v>7020185</v>
+        <v>7020329</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4375,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122699986</v>
+        <v>122700009</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4399,24 +4409,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525217</v>
+        <v>525066</v>
       </c>
       <c r="R37" t="n">
-        <v>7020178</v>
+        <v>7020292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4453,7 +4455,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4480,7 +4482,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122699997</v>
+        <v>122700004</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4520,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524808</v>
+        <v>525112</v>
       </c>
       <c r="R38" t="n">
-        <v>7020420</v>
+        <v>7020339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4589,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122699999</v>
+        <v>122700010</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4627,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524951</v>
+        <v>525061</v>
       </c>
       <c r="R39" t="n">
-        <v>7020351</v>
+        <v>7020296</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4696,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700009</v>
+        <v>122700002</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4734,10 +4736,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525066</v>
+        <v>525076</v>
       </c>
       <c r="R40" t="n">
-        <v>7020292</v>
+        <v>7020349</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700007</v>
+        <v>122700025</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525106</v>
+        <v>525407</v>
       </c>
       <c r="R41" t="n">
-        <v>7020311</v>
+        <v>7020146</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4877,11 +4879,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700030</v>
+        <v>122700037</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4924,21 +4921,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4948,10 +4945,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524857</v>
+        <v>524743</v>
       </c>
       <c r="R42" t="n">
-        <v>7020120</v>
+        <v>7020378</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5010,7 +5007,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700010</v>
+        <v>122700005</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5050,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525061</v>
+        <v>525103</v>
       </c>
       <c r="R43" t="n">
-        <v>7020296</v>
+        <v>7020335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5090,7 +5087,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,7 +5114,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122699996</v>
+        <v>122700001</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5157,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524805</v>
+        <v>525052</v>
       </c>
       <c r="R44" t="n">
-        <v>7020421</v>
+        <v>7020331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,10 +5221,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700028</v>
+        <v>122700036</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5264,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525342</v>
+        <v>524700</v>
       </c>
       <c r="R45" t="n">
-        <v>7020049</v>
+        <v>7020267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5326,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700006</v>
+        <v>122700024</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,16 +5339,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5366,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525089</v>
+        <v>524639</v>
       </c>
       <c r="R46" t="n">
-        <v>7020329</v>
+        <v>7020328</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5406,7 +5403,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5433,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700000</v>
+        <v>122700023</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5449,16 +5446,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5473,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524963</v>
+        <v>525274</v>
       </c>
       <c r="R47" t="n">
-        <v>7020373</v>
+        <v>7020074</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5513,7 +5510,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5540,7 +5537,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122700017</v>
+        <v>122699986</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5574,16 +5571,24 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524976</v>
+        <v>525217</v>
       </c>
       <c r="R48" t="n">
-        <v>7020218</v>
+        <v>7020178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5620,7 +5625,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5647,10 +5652,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700013</v>
+        <v>122700028</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524981</v>
+        <v>525342</v>
       </c>
       <c r="R49" t="n">
-        <v>7020231</v>
+        <v>7020049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700029</v>
+        <v>122700030</v>
       </c>
       <c r="B50" t="n">
         <v>79847</v>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525339</v>
+        <v>524857</v>
       </c>
       <c r="R50" t="n">
-        <v>7020046</v>
+        <v>7020120</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700027</v>
+        <v>122700033</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,21 +5872,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525364</v>
+        <v>525450</v>
       </c>
       <c r="R51" t="n">
-        <v>7020041</v>
+        <v>7019935</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700021</v>
+        <v>122700020</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525319</v>
+        <v>525498</v>
       </c>
       <c r="R52" t="n">
-        <v>7020073</v>
+        <v>7020014</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122699995</v>
+        <v>122699987</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524719</v>
+        <v>524637</v>
       </c>
       <c r="R2" t="n">
-        <v>7020350</v>
+        <v>7020366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122699991</v>
+        <v>122700027</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524850</v>
+        <v>525364</v>
       </c>
       <c r="R3" t="n">
-        <v>7020302</v>
+        <v>7020041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700034</v>
+        <v>122700012</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525015</v>
+        <v>524986</v>
       </c>
       <c r="R4" t="n">
-        <v>7019776</v>
+        <v>7020251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700013</v>
+        <v>122700021</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524981</v>
+        <v>525319</v>
       </c>
       <c r="R5" t="n">
-        <v>7020231</v>
+        <v>7020073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122700003</v>
+        <v>122700033</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525101</v>
+        <v>525450</v>
       </c>
       <c r="R6" t="n">
-        <v>7020350</v>
+        <v>7019935</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122699989</v>
+        <v>122700032</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524846</v>
+        <v>525024</v>
       </c>
       <c r="R7" t="n">
-        <v>7020185</v>
+        <v>7020263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122700014</v>
+        <v>122700030</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524981</v>
+        <v>524857</v>
       </c>
       <c r="R8" t="n">
-        <v>7020235</v>
+        <v>7020120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122699999</v>
+        <v>122700005</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1459,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524951</v>
+        <v>525103</v>
       </c>
       <c r="R9" t="n">
-        <v>7020351</v>
+        <v>7020335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700018</v>
+        <v>122700002</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1566,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525314</v>
+        <v>525076</v>
       </c>
       <c r="R10" t="n">
-        <v>7020173</v>
+        <v>7020349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700039</v>
+        <v>122700024</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525354</v>
+        <v>524639</v>
       </c>
       <c r="R11" t="n">
-        <v>7019963</v>
+        <v>7020328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122699988</v>
+        <v>122700013</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524640</v>
+        <v>524981</v>
       </c>
       <c r="R12" t="n">
-        <v>7020358</v>
+        <v>7020231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122700012</v>
+        <v>122700023</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,16 +1848,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524986</v>
+        <v>525274</v>
       </c>
       <c r="R13" t="n">
-        <v>7020251</v>
+        <v>7020074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122700007</v>
+        <v>122700000</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525106</v>
+        <v>524963</v>
       </c>
       <c r="R14" t="n">
-        <v>7020311</v>
+        <v>7020373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122700026</v>
+        <v>122700028</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525299</v>
+        <v>525342</v>
       </c>
       <c r="R15" t="n">
-        <v>7019885</v>
+        <v>7020049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122699987</v>
+        <v>122700008</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2198,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524637</v>
+        <v>525081</v>
       </c>
       <c r="R16" t="n">
-        <v>7020366</v>
+        <v>7020283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122699994</v>
+        <v>122700019</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2305,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524740</v>
+        <v>525451</v>
       </c>
       <c r="R17" t="n">
-        <v>7020346</v>
+        <v>7020169</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122699990</v>
+        <v>122700003</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2412,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524886</v>
+        <v>525101</v>
       </c>
       <c r="R18" t="n">
-        <v>7020196</v>
+        <v>7020350</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2442,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122699997</v>
+        <v>122700016</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2519,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524808</v>
+        <v>524970</v>
       </c>
       <c r="R19" t="n">
-        <v>7020420</v>
+        <v>7020222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122699996</v>
+        <v>122699999</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2626,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524805</v>
+        <v>524951</v>
       </c>
       <c r="R20" t="n">
-        <v>7020421</v>
+        <v>7020351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122700008</v>
+        <v>122699991</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2733,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525081</v>
+        <v>524850</v>
       </c>
       <c r="R21" t="n">
-        <v>7020283</v>
+        <v>7020302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122700021</v>
+        <v>122700004</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2840,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525319</v>
+        <v>525112</v>
       </c>
       <c r="R22" t="n">
-        <v>7020073</v>
+        <v>7020339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2870,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122699998</v>
+        <v>122700017</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2947,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524855</v>
+        <v>524976</v>
       </c>
       <c r="R23" t="n">
-        <v>7020387</v>
+        <v>7020218</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122699993</v>
+        <v>122700015</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3054,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524750</v>
+        <v>524981</v>
       </c>
       <c r="R24" t="n">
-        <v>7020358</v>
+        <v>7020235</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122700032</v>
+        <v>122699989</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525024</v>
+        <v>524846</v>
       </c>
       <c r="R25" t="n">
-        <v>7020263</v>
+        <v>7020185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122700031</v>
+        <v>122699995</v>
       </c>
       <c r="B26" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524640</v>
+        <v>524719</v>
       </c>
       <c r="R26" t="n">
-        <v>7020358</v>
+        <v>7020350</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122700035</v>
+        <v>122699992</v>
       </c>
       <c r="B27" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525057</v>
+        <v>524791</v>
       </c>
       <c r="R27" t="n">
-        <v>7020101</v>
+        <v>7020365</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122700016</v>
+        <v>122700022</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>90963</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3439,25 +3444,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524970</v>
+        <v>525086</v>
       </c>
       <c r="R28" t="n">
-        <v>7020222</v>
+        <v>7019775</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,11 +3508,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122699992</v>
+        <v>122700031</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524791</v>
+        <v>524640</v>
       </c>
       <c r="R29" t="n">
-        <v>7020365</v>
+        <v>7020358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3610,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3636,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122700019</v>
+        <v>122699993</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3681,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525451</v>
+        <v>524750</v>
       </c>
       <c r="R30" t="n">
-        <v>7020169</v>
+        <v>7020358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700017</v>
+        <v>122700039</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524976</v>
+        <v>525354</v>
       </c>
       <c r="R31" t="n">
-        <v>7020218</v>
+        <v>7019963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,11 +3819,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700000</v>
+        <v>122700029</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3861,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524963</v>
+        <v>525339</v>
       </c>
       <c r="R32" t="n">
-        <v>7020373</v>
+        <v>7020046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,11 +3921,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122700027</v>
+        <v>122699986</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,34 +3963,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525364</v>
+        <v>525217</v>
       </c>
       <c r="R33" t="n">
-        <v>7020041</v>
+        <v>7020178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4062,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122700022</v>
+        <v>122699988</v>
       </c>
       <c r="B34" t="n">
-        <v>90963</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4076,25 +4074,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525086</v>
+        <v>524640</v>
       </c>
       <c r="R34" t="n">
-        <v>7019775</v>
+        <v>7020358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122700029</v>
+        <v>122699998</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4182,21 +4185,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4206,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525339</v>
+        <v>524855</v>
       </c>
       <c r="R35" t="n">
-        <v>7020046</v>
+        <v>7020387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4242,6 +4245,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700006</v>
+        <v>122699997</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4308,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525089</v>
+        <v>524808</v>
       </c>
       <c r="R36" t="n">
-        <v>7020329</v>
+        <v>7020420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4375,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700009</v>
+        <v>122699996</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4415,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525066</v>
+        <v>524805</v>
       </c>
       <c r="R37" t="n">
-        <v>7020292</v>
+        <v>7020421</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700004</v>
+        <v>122700035</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,21 +4506,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525112</v>
+        <v>525057</v>
       </c>
       <c r="R38" t="n">
-        <v>7020339</v>
+        <v>7020101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4558,11 +4566,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4589,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700010</v>
+        <v>122700025</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4605,21 +4608,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4629,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525061</v>
+        <v>525407</v>
       </c>
       <c r="R39" t="n">
-        <v>7020296</v>
+        <v>7020146</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,11 +4668,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700002</v>
+        <v>122700026</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,21 +4710,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4736,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525076</v>
+        <v>525299</v>
       </c>
       <c r="R40" t="n">
-        <v>7020349</v>
+        <v>7019885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,11 +4770,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4803,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122700025</v>
+        <v>122700006</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,21 +4812,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4836,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525407</v>
+        <v>525089</v>
       </c>
       <c r="R41" t="n">
-        <v>7020146</v>
+        <v>7020329</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,6 +4872,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4905,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122700037</v>
+        <v>122700034</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4921,21 +4919,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4945,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524743</v>
+        <v>525015</v>
       </c>
       <c r="R42" t="n">
-        <v>7020378</v>
+        <v>7019776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5005,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122700005</v>
+        <v>122700009</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5047,10 +5045,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525103</v>
+        <v>525066</v>
       </c>
       <c r="R43" t="n">
-        <v>7020335</v>
+        <v>7020292</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5087,7 +5085,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5114,7 +5112,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122700001</v>
+        <v>122700020</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5154,10 +5152,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525052</v>
+        <v>525498</v>
       </c>
       <c r="R44" t="n">
-        <v>7020331</v>
+        <v>7020014</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122700036</v>
+        <v>122700018</v>
       </c>
       <c r="B45" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5237,21 +5235,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524700</v>
+        <v>525314</v>
       </c>
       <c r="R45" t="n">
-        <v>7020267</v>
+        <v>7020173</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5297,6 +5295,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5323,10 +5326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122700024</v>
+        <v>122699994</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5339,16 +5342,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5363,10 +5366,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524639</v>
+        <v>524740</v>
       </c>
       <c r="R46" t="n">
-        <v>7020328</v>
+        <v>7020346</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5403,7 +5406,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>äldre hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122700023</v>
+        <v>122700010</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5446,16 +5449,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5470,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525274</v>
+        <v>525061</v>
       </c>
       <c r="R47" t="n">
-        <v>7020074</v>
+        <v>7020296</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5510,7 +5513,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,7 +5540,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122699986</v>
+        <v>122700001</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5571,24 +5574,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525217</v>
+        <v>525052</v>
       </c>
       <c r="R48" t="n">
-        <v>7020178</v>
+        <v>7020331</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5652,10 +5647,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122700028</v>
+        <v>122700036</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5668,21 +5663,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525342</v>
+        <v>524700</v>
       </c>
       <c r="R49" t="n">
-        <v>7020049</v>
+        <v>7020267</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5754,10 +5749,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122700030</v>
+        <v>122699990</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5770,21 +5765,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5794,10 +5789,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524857</v>
+        <v>524886</v>
       </c>
       <c r="R50" t="n">
-        <v>7020120</v>
+        <v>7020196</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5830,6 +5825,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122700033</v>
+        <v>122700037</v>
       </c>
       <c r="B51" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,21 +5872,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525450</v>
+        <v>524743</v>
       </c>
       <c r="R51" t="n">
-        <v>7019935</v>
+        <v>7020378</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122700020</v>
+        <v>122700007</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525498</v>
+        <v>525106</v>
       </c>
       <c r="R52" t="n">
-        <v>7020014</v>
+        <v>7020311</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -3636,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122699993</v>
+        <v>122700039</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524750</v>
+        <v>525354</v>
       </c>
       <c r="R30" t="n">
-        <v>7020358</v>
+        <v>7019963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,11 +3712,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122700039</v>
+        <v>122699993</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3754,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3783,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525354</v>
+        <v>524750</v>
       </c>
       <c r="R31" t="n">
-        <v>7019963</v>
+        <v>7020358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,6 +3814,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122700029</v>
+        <v>122699986</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,34 +3861,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525339</v>
+        <v>525217</v>
       </c>
       <c r="R32" t="n">
-        <v>7020046</v>
+        <v>7020178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3921,6 +3929,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>bohål i asp 1,7m upp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122699986</v>
+        <v>122699988</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -3981,24 +3994,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nils-Erik bodlandet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525217</v>
+        <v>524640</v>
       </c>
       <c r="R33" t="n">
-        <v>7020178</v>
+        <v>7020358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,7 +4040,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>bohål i asp 1,7m upp.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122699988</v>
+        <v>122700029</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4078,21 +4083,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524640</v>
+        <v>525339</v>
       </c>
       <c r="R34" t="n">
-        <v>7020358</v>
+        <v>7020046</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4143,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -4169,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122699998</v>
+        <v>122700035</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524855</v>
+        <v>525057</v>
       </c>
       <c r="R35" t="n">
-        <v>7020387</v>
+        <v>7020101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4245,11 +4245,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,10 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122699997</v>
+        <v>122700025</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4292,21 +4287,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4316,10 +4311,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524808</v>
+        <v>525407</v>
       </c>
       <c r="R36" t="n">
-        <v>7020420</v>
+        <v>7020146</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4352,11 +4347,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,10 +4373,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122699996</v>
+        <v>122700026</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4389,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4423,10 +4413,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524805</v>
+        <v>525299</v>
       </c>
       <c r="R37" t="n">
-        <v>7020421</v>
+        <v>7019885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,11 +4449,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,10 +4475,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122700035</v>
+        <v>122699998</v>
       </c>
       <c r="B38" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,21 +4491,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4515,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525057</v>
+        <v>524855</v>
       </c>
       <c r="R38" t="n">
-        <v>7020101</v>
+        <v>7020387</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,6 +4551,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,10 +4582,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122700025</v>
+        <v>122699997</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,21 +4598,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,10 +4622,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525407</v>
+        <v>524808</v>
       </c>
       <c r="R39" t="n">
-        <v>7020146</v>
+        <v>7020420</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4668,6 +4658,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4694,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122700026</v>
+        <v>122699996</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4710,21 +4705,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525299</v>
+        <v>524805</v>
       </c>
       <c r="R40" t="n">
-        <v>7019885</v>
+        <v>7020421</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,6 +4765,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 2513-2025 artfynd.xlsx
+++ b/artfynd/A 2513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122699987</v>
+        <v>122700027</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524637</v>
+        <v>525364</v>
       </c>
       <c r="R2" t="n">
-        <v>7020366</v>
+        <v>7020041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700027</v>
+        <v>122700012</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525364</v>
+        <v>524986</v>
       </c>
       <c r="R3" t="n">
-        <v>7020041</v>
+        <v>7020251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700012</v>
+        <v>122700021</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524986</v>
+        <v>525319</v>
       </c>
       <c r="R4" t="n">
-        <v>7020251</v>
+        <v>7020073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700021</v>
+        <v>122699987</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525319</v>
+        <v>524637</v>
       </c>
       <c r="R5" t="n">
-        <v>7020073</v>
+        <v>7020366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -4169,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122700035</v>
+        <v>122699998</v>
       </c>
       <c r="B35" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525057</v>
+        <v>524855</v>
       </c>
       <c r="R35" t="n">
-        <v>7020101</v>
+        <v>7020387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4245,6 +4245,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,10 +4276,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122700025</v>
+        <v>122699997</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4287,21 +4292,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4311,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525407</v>
+        <v>524808</v>
       </c>
       <c r="R36" t="n">
-        <v>7020146</v>
+        <v>7020420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4347,6 +4352,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4373,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122700026</v>
+        <v>122699996</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4389,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4413,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525299</v>
+        <v>524805</v>
       </c>
       <c r="R37" t="n">
-        <v>7019885</v>
+        <v>7020421</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,6 +4459,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122699998</v>
+        <v>122700035</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,21 +4506,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4515,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524855</v>
+        <v>525057</v>
       </c>
       <c r="R38" t="n">
-        <v>7020387</v>
+        <v>7020101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4551,11 +4566,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4582,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122699997</v>
+        <v>122700025</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4598,21 +4608,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4622,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524808</v>
+        <v>525407</v>
       </c>
       <c r="R39" t="n">
-        <v>7020420</v>
+        <v>7020146</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,11 +4668,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4689,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122699996</v>
+        <v>122700026</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,21 +4710,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4729,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524805</v>
+        <v>525299</v>
       </c>
       <c r="R40" t="n">
-        <v>7020421</v>
+        <v>7019885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4765,11 +4770,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
